--- a/research/traditional_assets/database/data/estonia/estonia_power.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_power.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06928487337826285</v>
+        <v>0.06918230363150632</v>
       </c>
       <c r="C2">
-        <v>1999.501076462573</v>
+        <v>1982.69547925505</v>
       </c>
       <c r="D2">
-        <v>1892.601076462573</v>
+        <v>1895.58347925505</v>
       </c>
       <c r="E2">
-        <v>-1072.3</v>
+        <v>-1052.512</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.788</v>
       </c>
       <c r="G2">
         <v>106.9</v>
@@ -1439,28 +1439,28 @@
         <v>174.175</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9953364</v>
       </c>
       <c r="N2">
-        <v>174.175</v>
+        <v>173.1796636</v>
       </c>
       <c r="O2">
-        <v>34.835</v>
+        <v>34.63593271999999</v>
       </c>
       <c r="P2">
-        <v>139.34</v>
+        <v>138.54373088</v>
       </c>
       <c r="Q2">
-        <v>168.04</v>
+        <v>167.24373088</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06928487337826285</v>
+        <v>0.06947465013283467</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.449099364695417</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>174.991088440049</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06918230363150632</v>
+        <v>0.06907973388474979</v>
       </c>
       <c r="C3">
-        <v>1982.69547925505</v>
+        <v>1965.899296355864</v>
       </c>
       <c r="D3">
-        <v>1895.58347925505</v>
+        <v>1898.575296355864</v>
       </c>
       <c r="E3">
-        <v>-1052.512</v>
+        <v>-1032.724</v>
       </c>
       <c r="F3">
-        <v>19.788</v>
+        <v>39.576</v>
       </c>
       <c r="G3">
         <v>106.9</v>
@@ -1521,28 +1521,28 @@
         <v>174.175</v>
       </c>
       <c r="M3">
-        <v>0.9953364</v>
+        <v>1.9906728</v>
       </c>
       <c r="N3">
-        <v>173.1796636</v>
+        <v>172.1843272</v>
       </c>
       <c r="O3">
-        <v>34.63593271999999</v>
+        <v>34.43686544</v>
       </c>
       <c r="P3">
-        <v>138.54373088</v>
+        <v>137.74746176</v>
       </c>
       <c r="Q3">
-        <v>167.24373088</v>
+        <v>166.44746176</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06947465013283467</v>
+        <v>0.06966829988239776</v>
       </c>
       <c r="T3">
-        <v>0.449099364695417</v>
+        <v>0.4527728288866191</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>174.991088440049</v>
+        <v>87.4955442200245</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06907973388474979</v>
+        <v>0.06897716413799326</v>
       </c>
       <c r="C4">
-        <v>1965.899296355864</v>
+        <v>1949.112572411553</v>
       </c>
       <c r="D4">
-        <v>1898.575296355864</v>
+        <v>1901.576572411553</v>
       </c>
       <c r="E4">
-        <v>-1032.724</v>
+        <v>-1012.936</v>
       </c>
       <c r="F4">
-        <v>39.576</v>
+        <v>59.364</v>
       </c>
       <c r="G4">
         <v>106.9</v>
@@ -1603,28 +1603,28 @@
         <v>174.175</v>
       </c>
       <c r="M4">
-        <v>1.9906728</v>
+        <v>2.9860092</v>
       </c>
       <c r="N4">
-        <v>172.1843272</v>
+        <v>171.1889908</v>
       </c>
       <c r="O4">
-        <v>34.43686544</v>
+        <v>34.23779816</v>
       </c>
       <c r="P4">
-        <v>137.74746176</v>
+        <v>136.95119264</v>
       </c>
       <c r="Q4">
-        <v>166.44746176</v>
+        <v>165.65119264</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06966829988239776</v>
+        <v>0.06986594241030233</v>
       </c>
       <c r="T4">
-        <v>0.4527728288866191</v>
+        <v>0.4565220346075367</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>87.4955442200245</v>
+        <v>58.33036281334967</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06897716413799326</v>
+        <v>0.06887459439123675</v>
       </c>
       <c r="C5">
-        <v>1949.112572411553</v>
+        <v>1932.335352351412</v>
       </c>
       <c r="D5">
-        <v>1901.576572411553</v>
+        <v>1904.587352351412</v>
       </c>
       <c r="E5">
-        <v>-1012.936</v>
+        <v>-993.1479999999999</v>
       </c>
       <c r="F5">
-        <v>59.364</v>
+        <v>79.152</v>
       </c>
       <c r="G5">
         <v>106.9</v>
@@ -1685,28 +1685,28 @@
         <v>174.175</v>
       </c>
       <c r="M5">
-        <v>2.9860092</v>
+        <v>3.9813456</v>
       </c>
       <c r="N5">
-        <v>171.1889908</v>
+        <v>170.1936544</v>
       </c>
       <c r="O5">
-        <v>34.23779816</v>
+        <v>34.03873088</v>
       </c>
       <c r="P5">
-        <v>136.95119264</v>
+        <v>136.15492352</v>
       </c>
       <c r="Q5">
-        <v>165.65119264</v>
+        <v>164.85492352</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06986594241030233</v>
+        <v>0.07006770249087162</v>
       </c>
       <c r="T5">
-        <v>0.4565220346075367</v>
+        <v>0.4603493487809736</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>58.33036281334967</v>
+        <v>43.74777211001225</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06887459439123675</v>
+        <v>0.06877202464448022</v>
       </c>
       <c r="C6">
-        <v>1932.335352351412</v>
+        <v>1915.567681389736</v>
       </c>
       <c r="D6">
-        <v>1904.587352351412</v>
+        <v>1907.607681389736</v>
       </c>
       <c r="E6">
-        <v>-993.1479999999999</v>
+        <v>-973.3599999999999</v>
       </c>
       <c r="F6">
-        <v>79.152</v>
+        <v>98.94</v>
       </c>
       <c r="G6">
         <v>106.9</v>
@@ -1767,28 +1767,28 @@
         <v>174.175</v>
       </c>
       <c r="M6">
-        <v>3.9813456</v>
+        <v>4.976681999999999</v>
       </c>
       <c r="N6">
-        <v>170.1936544</v>
+        <v>169.198318</v>
       </c>
       <c r="O6">
-        <v>34.03873088</v>
+        <v>33.83966359999999</v>
       </c>
       <c r="P6">
-        <v>136.15492352</v>
+        <v>135.3586544</v>
       </c>
       <c r="Q6">
-        <v>164.85492352</v>
+        <v>164.0586544</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07006770249087162</v>
+        <v>0.07027371015208445</v>
       </c>
       <c r="T6">
-        <v>0.4603493487809736</v>
+        <v>0.4642572379896405</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.74777211001225</v>
+        <v>34.9982176880098</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06877202464448022</v>
+        <v>0.06866945489772369</v>
       </c>
       <c r="C7">
-        <v>1915.567681389736</v>
+        <v>1898.809605028079</v>
       </c>
       <c r="D7">
-        <v>1907.607681389736</v>
+        <v>1910.637605028079</v>
       </c>
       <c r="E7">
-        <v>-973.3599999999999</v>
+        <v>-953.5719999999999</v>
       </c>
       <c r="F7">
-        <v>98.94</v>
+        <v>118.728</v>
       </c>
       <c r="G7">
         <v>106.9</v>
@@ -1849,28 +1849,28 @@
         <v>174.175</v>
       </c>
       <c r="M7">
-        <v>4.976681999999999</v>
+        <v>5.972018400000001</v>
       </c>
       <c r="N7">
-        <v>169.198318</v>
+        <v>168.2029816</v>
       </c>
       <c r="O7">
-        <v>33.83966359999999</v>
+        <v>33.64059632</v>
       </c>
       <c r="P7">
-        <v>135.3586544</v>
+        <v>134.56238528</v>
       </c>
       <c r="Q7">
-        <v>164.0586544</v>
+        <v>163.26238528</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07027371015208445</v>
+        <v>0.07048410095502521</v>
       </c>
       <c r="T7">
-        <v>0.4642572379896405</v>
+        <v>0.4682482737772154</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.9982176880098</v>
+        <v>29.16518140667483</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06866945489772369</v>
+        <v>0.06856688515096716</v>
       </c>
       <c r="C8">
-        <v>1898.809605028079</v>
+        <v>1882.061169057545</v>
       </c>
       <c r="D8">
-        <v>1910.637605028079</v>
+        <v>1913.677169057545</v>
       </c>
       <c r="E8">
-        <v>-953.572</v>
+        <v>-933.784</v>
       </c>
       <c r="F8">
-        <v>118.728</v>
+        <v>138.516</v>
       </c>
       <c r="G8">
         <v>106.9</v>
@@ -1931,28 +1931,28 @@
         <v>174.175</v>
       </c>
       <c r="M8">
-        <v>5.9720184</v>
+        <v>6.967354799999999</v>
       </c>
       <c r="N8">
-        <v>168.2029816</v>
+        <v>167.2076452</v>
       </c>
       <c r="O8">
-        <v>33.64059632</v>
+        <v>33.44152904</v>
       </c>
       <c r="P8">
-        <v>134.56238528</v>
+        <v>133.76611616</v>
       </c>
       <c r="Q8">
-        <v>163.26238528</v>
+        <v>162.46611616</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07048410095502521</v>
+        <v>0.07069901629136255</v>
       </c>
       <c r="T8">
-        <v>0.4682482737772154</v>
+        <v>0.4723251382914047</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.16518140667484</v>
+        <v>24.998726920007</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06856688515096716</v>
+        <v>0.06846431540421065</v>
       </c>
       <c r="C9">
-        <v>1882.061169057545</v>
+        <v>1865.32241956109</v>
       </c>
       <c r="D9">
-        <v>1913.677169057545</v>
+        <v>1916.72641956109</v>
       </c>
       <c r="E9">
-        <v>-933.7839999999999</v>
+        <v>-913.996</v>
       </c>
       <c r="F9">
-        <v>138.516</v>
+        <v>158.304</v>
       </c>
       <c r="G9">
         <v>106.9</v>
@@ -2013,28 +2013,28 @@
         <v>174.175</v>
       </c>
       <c r="M9">
-        <v>6.967354800000001</v>
+        <v>7.9626912</v>
       </c>
       <c r="N9">
-        <v>167.2076452</v>
+        <v>166.2123088</v>
       </c>
       <c r="O9">
-        <v>33.44152904</v>
+        <v>33.24246176</v>
       </c>
       <c r="P9">
-        <v>133.76611616</v>
+        <v>132.96984704</v>
       </c>
       <c r="Q9">
-        <v>162.46611616</v>
+        <v>161.66984704</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07069901629136255</v>
+        <v>0.07091860370022895</v>
       </c>
       <c r="T9">
-        <v>0.4723251382914047</v>
+        <v>0.4764906302950329</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.99872692000699</v>
+        <v>21.87388605500612</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06846431540421065</v>
+        <v>0.06836174565745412</v>
       </c>
       <c r="C10">
-        <v>1865.32241956109</v>
+        <v>1848.593402915855</v>
       </c>
       <c r="D10">
-        <v>1916.72641956109</v>
+        <v>1919.785402915855</v>
       </c>
       <c r="E10">
-        <v>-913.996</v>
+        <v>-894.208</v>
       </c>
       <c r="F10">
-        <v>158.304</v>
+        <v>178.092</v>
       </c>
       <c r="G10">
         <v>106.9</v>
@@ -2095,28 +2095,28 @@
         <v>174.175</v>
       </c>
       <c r="M10">
-        <v>7.9626912</v>
+        <v>8.958027599999999</v>
       </c>
       <c r="N10">
-        <v>166.2123088</v>
+        <v>165.2169724</v>
       </c>
       <c r="O10">
-        <v>33.24246176</v>
+        <v>33.04339448</v>
       </c>
       <c r="P10">
-        <v>132.96984704</v>
+        <v>132.17357792</v>
       </c>
       <c r="Q10">
-        <v>161.66984704</v>
+        <v>160.87357792</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07091860370022895</v>
+        <v>0.07114301720599353</v>
       </c>
       <c r="T10">
-        <v>0.4764906302950329</v>
+        <v>0.4807476715734661</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.87388605500612</v>
+        <v>19.44345427111655</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06836174565745412</v>
+        <v>0.06825917591069759</v>
       </c>
       <c r="C11">
-        <v>1848.593402915855</v>
+        <v>1831.874165795512</v>
       </c>
       <c r="D11">
-        <v>1919.785402915855</v>
+        <v>1922.854165795512</v>
       </c>
       <c r="E11">
-        <v>-894.208</v>
+        <v>-874.42</v>
       </c>
       <c r="F11">
-        <v>178.092</v>
+        <v>197.88</v>
       </c>
       <c r="G11">
         <v>106.9</v>
@@ -2177,28 +2177,28 @@
         <v>174.175</v>
       </c>
       <c r="M11">
-        <v>8.958027599999999</v>
+        <v>9.953363999999997</v>
       </c>
       <c r="N11">
-        <v>165.2169724</v>
+        <v>164.221636</v>
       </c>
       <c r="O11">
-        <v>33.04339448</v>
+        <v>32.8443272</v>
       </c>
       <c r="P11">
-        <v>132.17357792</v>
+        <v>131.3773088</v>
       </c>
       <c r="Q11">
-        <v>160.87357792</v>
+        <v>160.0773088</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07114301720599353</v>
+        <v>0.07137241767855287</v>
       </c>
       <c r="T11">
-        <v>0.4807476715734661</v>
+        <v>0.4850993137691978</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.44345427111655</v>
+        <v>17.4991088440049</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06825917591069761</v>
+        <v>0.06815660616394106</v>
       </c>
       <c r="C12">
-        <v>1831.874165795512</v>
+        <v>1815.164755172645</v>
       </c>
       <c r="D12">
-        <v>1922.854165795512</v>
+        <v>1925.932755172645</v>
       </c>
       <c r="E12">
-        <v>-874.42</v>
+        <v>-854.6319999999999</v>
       </c>
       <c r="F12">
-        <v>197.88</v>
+        <v>217.668</v>
       </c>
       <c r="G12">
         <v>106.9</v>
@@ -2259,28 +2259,28 @@
         <v>174.175</v>
       </c>
       <c r="M12">
-        <v>9.953363999999999</v>
+        <v>10.9487004</v>
       </c>
       <c r="N12">
-        <v>164.221636</v>
+        <v>163.2262996</v>
       </c>
       <c r="O12">
-        <v>32.8443272</v>
+        <v>32.64525991999999</v>
       </c>
       <c r="P12">
-        <v>131.3773088</v>
+        <v>130.58103968</v>
       </c>
       <c r="Q12">
-        <v>160.0773088</v>
+        <v>159.28103968</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07137241767855289</v>
+        <v>0.0716069732179113</v>
       </c>
       <c r="T12">
-        <v>0.485099313769198</v>
+        <v>0.4895487456771933</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.4991088440049</v>
+        <v>15.90828076727718</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06815660616394106</v>
+        <v>0.06805403641718454</v>
       </c>
       <c r="C13">
-        <v>1815.164755172645</v>
+        <v>1798.465218321139</v>
       </c>
       <c r="D13">
-        <v>1925.932755172645</v>
+        <v>1929.021218321139</v>
       </c>
       <c r="E13">
-        <v>-854.6319999999999</v>
+        <v>-834.8439999999999</v>
       </c>
       <c r="F13">
-        <v>217.668</v>
+        <v>237.456</v>
       </c>
       <c r="G13">
         <v>106.9</v>
@@ -2341,28 +2341,28 @@
         <v>174.175</v>
       </c>
       <c r="M13">
-        <v>10.9487004</v>
+        <v>11.9440368</v>
       </c>
       <c r="N13">
-        <v>163.2262996</v>
+        <v>162.2309632</v>
       </c>
       <c r="O13">
-        <v>32.64525991999999</v>
+        <v>32.44619264</v>
       </c>
       <c r="P13">
-        <v>130.58103968</v>
+        <v>129.78477056</v>
       </c>
       <c r="Q13">
-        <v>159.28103968</v>
+        <v>158.48477056</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0716069732179113</v>
+        <v>0.07184685956498243</v>
       </c>
       <c r="T13">
-        <v>0.4895487456771933</v>
+        <v>0.4940993010376432</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.90828076727718</v>
+        <v>14.58259070333742</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06805403641718454</v>
+        <v>0.06795146667042801</v>
       </c>
       <c r="C14">
-        <v>1798.465218321139</v>
+        <v>1781.775602818604</v>
       </c>
       <c r="D14">
-        <v>1929.021218321139</v>
+        <v>1932.119602818604</v>
       </c>
       <c r="E14">
-        <v>-834.8439999999999</v>
+        <v>-815.0559999999999</v>
       </c>
       <c r="F14">
-        <v>237.456</v>
+        <v>257.244</v>
       </c>
       <c r="G14">
         <v>106.9</v>
@@ -2423,28 +2423,28 @@
         <v>174.175</v>
       </c>
       <c r="M14">
-        <v>11.9440368</v>
+        <v>12.9393732</v>
       </c>
       <c r="N14">
-        <v>162.2309632</v>
+        <v>161.2356268</v>
       </c>
       <c r="O14">
-        <v>32.44619264</v>
+        <v>32.24712536</v>
       </c>
       <c r="P14">
-        <v>129.78477056</v>
+        <v>128.98850144</v>
       </c>
       <c r="Q14">
-        <v>158.48477056</v>
+        <v>157.68850144</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07184685956498243</v>
+        <v>0.07209226054072185</v>
       </c>
       <c r="T14">
-        <v>0.4940993010376432</v>
+        <v>0.4987544668661493</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.58259070333742</v>
+        <v>13.46085295692684</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06795146667042801</v>
+        <v>0.06801689692367149</v>
       </c>
       <c r="C15">
-        <v>1781.775602818604</v>
+        <v>1760.009964458866</v>
       </c>
       <c r="D15">
-        <v>1932.119602818604</v>
+        <v>1930.141964458866</v>
       </c>
       <c r="E15">
-        <v>-815.0559999999999</v>
+        <v>-795.2679999999999</v>
       </c>
       <c r="F15">
-        <v>257.244</v>
+        <v>277.032</v>
       </c>
       <c r="G15">
         <v>106.9</v>
@@ -2505,45 +2505,45 @@
         <v>174.175</v>
       </c>
       <c r="M15">
-        <v>12.9393732</v>
+        <v>14.3502576</v>
       </c>
       <c r="N15">
-        <v>161.2356268</v>
+        <v>159.8247424</v>
       </c>
       <c r="O15">
-        <v>32.24712536</v>
+        <v>31.96494848</v>
       </c>
       <c r="P15">
-        <v>128.98850144</v>
+        <v>127.85979392</v>
       </c>
       <c r="Q15">
-        <v>157.68850144</v>
+        <v>156.55979392</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07209226054072185</v>
+        <v>0.07234336851589708</v>
       </c>
       <c r="T15">
-        <v>0.4987544668661493</v>
+        <v>0.5035178923650858</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.46085295692684</v>
+        <v>12.13741278065977</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06801689692367149</v>
+        <v>0.06792632717691496</v>
       </c>
       <c r="C16">
-        <v>1760.009964458866</v>
+        <v>1742.960525548237</v>
       </c>
       <c r="D16">
-        <v>1930.141964458866</v>
+        <v>1932.880525548237</v>
       </c>
       <c r="E16">
-        <v>-795.2679999999999</v>
+        <v>-775.4799999999999</v>
       </c>
       <c r="F16">
-        <v>277.032</v>
+        <v>296.8200000000001</v>
       </c>
       <c r="G16">
         <v>106.9</v>
@@ -2587,28 +2587,28 @@
         <v>174.175</v>
       </c>
       <c r="M16">
-        <v>14.3502576</v>
+        <v>15.375276</v>
       </c>
       <c r="N16">
-        <v>159.8247424</v>
+        <v>158.799724</v>
       </c>
       <c r="O16">
-        <v>31.96494848</v>
+        <v>31.7599448</v>
       </c>
       <c r="P16">
-        <v>127.85979392</v>
+        <v>127.0397792</v>
       </c>
       <c r="Q16">
-        <v>156.55979392</v>
+        <v>155.7397792</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07234336851589708</v>
+        <v>0.0726003849140176</v>
       </c>
       <c r="T16">
-        <v>0.5035178923650858</v>
+        <v>0.5083933984639973</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.13741278065977</v>
+        <v>11.32825192861578</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06792632717691496</v>
+        <v>0.06783575743015843</v>
       </c>
       <c r="C17">
-        <v>1742.960525548237</v>
+        <v>1725.91886883497</v>
       </c>
       <c r="D17">
-        <v>1932.880525548237</v>
+        <v>1935.62686883497</v>
       </c>
       <c r="E17">
-        <v>-775.48</v>
+        <v>-755.692</v>
       </c>
       <c r="F17">
-        <v>296.82</v>
+        <v>316.608</v>
       </c>
       <c r="G17">
         <v>106.9</v>
@@ -2669,28 +2669,28 @@
         <v>174.175</v>
       </c>
       <c r="M17">
-        <v>15.375276</v>
+        <v>16.4002944</v>
       </c>
       <c r="N17">
-        <v>158.799724</v>
+        <v>157.7747056</v>
       </c>
       <c r="O17">
-        <v>31.7599448</v>
+        <v>31.55494112</v>
       </c>
       <c r="P17">
-        <v>127.0397792</v>
+        <v>126.21976448</v>
       </c>
       <c r="Q17">
-        <v>155.7397792</v>
+        <v>154.91976448</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0726003849140176</v>
+        <v>0.07286352075018862</v>
       </c>
       <c r="T17">
-        <v>0.5083933984639973</v>
+        <v>0.5133849880414543</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.32825192861578</v>
+        <v>10.6202361830773</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06783575743015843</v>
+        <v>0.06774518768340192</v>
       </c>
       <c r="C18">
-        <v>1725.91886883497</v>
+        <v>1708.88502753839</v>
       </c>
       <c r="D18">
-        <v>1935.62686883497</v>
+        <v>1938.381027538389</v>
       </c>
       <c r="E18">
-        <v>-755.692</v>
+        <v>-735.904</v>
       </c>
       <c r="F18">
-        <v>316.608</v>
+        <v>336.396</v>
       </c>
       <c r="G18">
         <v>106.9</v>
@@ -2751,28 +2751,28 @@
         <v>174.175</v>
       </c>
       <c r="M18">
-        <v>16.4002944</v>
+        <v>17.4253128</v>
       </c>
       <c r="N18">
-        <v>157.7747056</v>
+        <v>156.7496872</v>
       </c>
       <c r="O18">
-        <v>31.55494112</v>
+        <v>31.34993744</v>
       </c>
       <c r="P18">
-        <v>126.21976448</v>
+        <v>125.39974976</v>
       </c>
       <c r="Q18">
-        <v>154.91976448</v>
+        <v>154.09974976</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07286352075018862</v>
+        <v>0.07313299720891797</v>
       </c>
       <c r="T18">
-        <v>0.5133849880414543</v>
+        <v>0.518496856885838</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.6202361830773</v>
+        <v>9.995516407602162</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06774518768340192</v>
+        <v>0.06789941793664539</v>
       </c>
       <c r="C19">
-        <v>1708.88502753839</v>
+        <v>1684.411679409422</v>
       </c>
       <c r="D19">
-        <v>1938.381027538389</v>
+        <v>1933.695679409422</v>
       </c>
       <c r="E19">
-        <v>-735.904</v>
+        <v>-716.116</v>
       </c>
       <c r="F19">
-        <v>336.396</v>
+        <v>356.184</v>
       </c>
       <c r="G19">
         <v>106.9</v>
@@ -2833,45 +2833,45 @@
         <v>174.175</v>
       </c>
       <c r="M19">
-        <v>17.4253128</v>
+        <v>19.055844</v>
       </c>
       <c r="N19">
-        <v>156.7496872</v>
+        <v>155.119156</v>
       </c>
       <c r="O19">
-        <v>31.34993744</v>
+        <v>31.0238312</v>
       </c>
       <c r="P19">
-        <v>125.39974976</v>
+        <v>124.0953248</v>
       </c>
       <c r="Q19">
-        <v>154.09974976</v>
+        <v>152.7953248</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07313299720891797</v>
+        <v>0.07340904626420169</v>
       </c>
       <c r="T19">
-        <v>0.518496856885838</v>
+        <v>0.5237334054581336</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.995516407602162</v>
+        <v>9.140240652683763</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06789941793664539</v>
+        <v>0.06782244818988886</v>
       </c>
       <c r="C20">
-        <v>1684.411679409422</v>
+        <v>1666.95910229004</v>
       </c>
       <c r="D20">
-        <v>1933.695679409422</v>
+        <v>1936.03110229004</v>
       </c>
       <c r="E20">
-        <v>-716.116</v>
+        <v>-696.328</v>
       </c>
       <c r="F20">
-        <v>356.184</v>
+        <v>375.972</v>
       </c>
       <c r="G20">
         <v>106.9</v>
@@ -2915,28 +2915,28 @@
         <v>174.175</v>
       </c>
       <c r="M20">
-        <v>19.055844</v>
+        <v>20.114502</v>
       </c>
       <c r="N20">
-        <v>155.119156</v>
+        <v>154.060498</v>
       </c>
       <c r="O20">
-        <v>31.0238312</v>
+        <v>30.8120996</v>
       </c>
       <c r="P20">
-        <v>124.0953248</v>
+        <v>123.2483984</v>
       </c>
       <c r="Q20">
-        <v>152.7953248</v>
+        <v>151.9483984</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07340904626420169</v>
+        <v>0.0736919113455418</v>
       </c>
       <c r="T20">
-        <v>0.5237334054581335</v>
+        <v>0.5290992515260413</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.140240652683765</v>
+        <v>8.659175355174092</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06782244818988886</v>
+        <v>0.06774547844313233</v>
       </c>
       <c r="C21">
-        <v>1666.95910229004</v>
+        <v>1649.5121732107</v>
       </c>
       <c r="D21">
-        <v>1936.03110229004</v>
+        <v>1938.3721732107</v>
       </c>
       <c r="E21">
-        <v>-696.328</v>
+        <v>-676.54</v>
       </c>
       <c r="F21">
-        <v>375.972</v>
+        <v>395.76</v>
       </c>
       <c r="G21">
         <v>106.9</v>
@@ -2997,28 +2997,28 @@
         <v>174.175</v>
       </c>
       <c r="M21">
-        <v>20.114502</v>
+        <v>21.17316</v>
       </c>
       <c r="N21">
-        <v>154.060498</v>
+        <v>153.00184</v>
       </c>
       <c r="O21">
-        <v>30.8120996</v>
+        <v>30.600368</v>
       </c>
       <c r="P21">
-        <v>123.2483984</v>
+        <v>122.401472</v>
       </c>
       <c r="Q21">
-        <v>151.9483984</v>
+        <v>151.101472</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0736919113455418</v>
+        <v>0.07398184805391542</v>
       </c>
       <c r="T21">
-        <v>0.5290992515260413</v>
+        <v>0.5345992437456466</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.659175355174092</v>
+        <v>8.226216587415387</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06774547844313233</v>
+        <v>0.06766850869637581</v>
       </c>
       <c r="C22">
-        <v>1649.5121732107</v>
+        <v>1632.07091268523</v>
       </c>
       <c r="D22">
-        <v>1938.3721732107</v>
+        <v>1940.718912685229</v>
       </c>
       <c r="E22">
-        <v>-676.54</v>
+        <v>-656.752</v>
       </c>
       <c r="F22">
-        <v>395.76</v>
+        <v>415.548</v>
       </c>
       <c r="G22">
         <v>106.9</v>
@@ -3079,28 +3079,28 @@
         <v>174.175</v>
       </c>
       <c r="M22">
-        <v>21.17316</v>
+        <v>22.231818</v>
       </c>
       <c r="N22">
-        <v>153.00184</v>
+        <v>151.943182</v>
       </c>
       <c r="O22">
-        <v>30.600368</v>
+        <v>30.3886364</v>
       </c>
       <c r="P22">
-        <v>122.401472</v>
+        <v>121.5545456</v>
       </c>
       <c r="Q22">
-        <v>151.101472</v>
+        <v>150.2545456</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07398184805391542</v>
+        <v>0.07427912493212127</v>
       </c>
       <c r="T22">
-        <v>0.5345992437456466</v>
+        <v>0.5402384762746092</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.226216587415387</v>
+        <v>7.834491988014654</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06766850869637581</v>
+        <v>0.06773233894961929</v>
       </c>
       <c r="C23">
-        <v>1632.07091268523</v>
+        <v>1610.336382930846</v>
       </c>
       <c r="D23">
-        <v>1940.718912685229</v>
+        <v>1938.772382930846</v>
       </c>
       <c r="E23">
-        <v>-656.752</v>
+        <v>-636.9639999999999</v>
       </c>
       <c r="F23">
-        <v>415.548</v>
+        <v>435.336</v>
       </c>
       <c r="G23">
         <v>106.9</v>
@@ -3161,45 +3161,45 @@
         <v>174.175</v>
       </c>
       <c r="M23">
-        <v>22.231818</v>
+        <v>23.6387448</v>
       </c>
       <c r="N23">
-        <v>151.943182</v>
+        <v>150.5362552</v>
       </c>
       <c r="O23">
-        <v>30.3886364</v>
+        <v>30.10725103999999</v>
       </c>
       <c r="P23">
-        <v>121.5545456</v>
+        <v>120.42900416</v>
       </c>
       <c r="Q23">
-        <v>150.2545456</v>
+        <v>149.12900416</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07427912493212127</v>
+        <v>0.0745840242943837</v>
       </c>
       <c r="T23">
-        <v>0.5402384762746092</v>
+        <v>0.5460223045094426</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.834491988014654</v>
+        <v>7.368200023886208</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06773233894961929</v>
+        <v>0.06766176920286276</v>
       </c>
       <c r="C24">
-        <v>1610.336382930846</v>
+        <v>1592.7006644614</v>
       </c>
       <c r="D24">
-        <v>1938.772382930846</v>
+        <v>1940.9246644614</v>
       </c>
       <c r="E24">
-        <v>-636.9639999999999</v>
+        <v>-617.1759999999999</v>
       </c>
       <c r="F24">
-        <v>435.336</v>
+        <v>455.124</v>
       </c>
       <c r="G24">
         <v>106.9</v>
@@ -3243,28 +3243,28 @@
         <v>174.175</v>
       </c>
       <c r="M24">
-        <v>23.6387448</v>
+        <v>24.7132332</v>
       </c>
       <c r="N24">
-        <v>150.5362552</v>
+        <v>149.4617668</v>
       </c>
       <c r="O24">
-        <v>30.10725103999999</v>
+        <v>29.89235336</v>
       </c>
       <c r="P24">
-        <v>120.42900416</v>
+        <v>119.56941344</v>
       </c>
       <c r="Q24">
-        <v>149.12900416</v>
+        <v>148.26941344</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0745840242943837</v>
+        <v>0.07489684312060099</v>
       </c>
       <c r="T24">
-        <v>0.5460223045094426</v>
+        <v>0.5519563620490768</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.368200023886208</v>
+        <v>7.047843501108547</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06766176920286276</v>
+        <v>0.06759119945610624</v>
       </c>
       <c r="C25">
-        <v>1592.7006644614</v>
+        <v>1575.069729909856</v>
       </c>
       <c r="D25">
-        <v>1940.9246644614</v>
+        <v>1943.081729909856</v>
       </c>
       <c r="E25">
-        <v>-617.1759999999999</v>
+        <v>-597.3879999999999</v>
       </c>
       <c r="F25">
-        <v>455.124</v>
+        <v>474.912</v>
       </c>
       <c r="G25">
         <v>106.9</v>
@@ -3325,28 +3325,28 @@
         <v>174.175</v>
       </c>
       <c r="M25">
-        <v>24.7132332</v>
+        <v>25.7877216</v>
       </c>
       <c r="N25">
-        <v>149.4617668</v>
+        <v>148.3872784</v>
       </c>
       <c r="O25">
-        <v>29.89235336</v>
+        <v>29.67745568</v>
       </c>
       <c r="P25">
-        <v>119.56941344</v>
+        <v>118.70982272</v>
       </c>
       <c r="Q25">
-        <v>148.26941344</v>
+        <v>147.40982272</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07489684312060099</v>
+        <v>0.07521789402119242</v>
       </c>
       <c r="T25">
-        <v>0.5519563620490768</v>
+        <v>0.5580465789976488</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.047843501108547</v>
+        <v>6.754183355229024</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06759119945610624</v>
+        <v>0.06752062970934972</v>
       </c>
       <c r="C26">
-        <v>1575.069729909856</v>
+        <v>1557.443595243921</v>
       </c>
       <c r="D26">
-        <v>1943.081729909856</v>
+        <v>1945.243595243921</v>
       </c>
       <c r="E26">
-        <v>-597.3879999999999</v>
+        <v>-577.5999999999999</v>
       </c>
       <c r="F26">
-        <v>474.912</v>
+        <v>494.7</v>
       </c>
       <c r="G26">
         <v>106.9</v>
@@ -3407,28 +3407,28 @@
         <v>174.175</v>
       </c>
       <c r="M26">
-        <v>25.7877216</v>
+        <v>26.86221</v>
       </c>
       <c r="N26">
-        <v>148.3872784</v>
+        <v>147.31279</v>
       </c>
       <c r="O26">
-        <v>29.67745568</v>
+        <v>29.462558</v>
       </c>
       <c r="P26">
-        <v>118.70982272</v>
+        <v>117.850232</v>
       </c>
       <c r="Q26">
-        <v>147.40982272</v>
+        <v>146.550232</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07521789402119242</v>
+        <v>0.07554750627913294</v>
       </c>
       <c r="T26">
-        <v>0.5580465789976486</v>
+        <v>0.5642992017315159</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.754183355229025</v>
+        <v>6.484016021019863</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06752062970934972</v>
+        <v>0.06745005996259319</v>
       </c>
       <c r="C27">
-        <v>1557.443595243921</v>
+        <v>1539.822276502443</v>
       </c>
       <c r="D27">
-        <v>1945.243595243921</v>
+        <v>1947.410276502443</v>
       </c>
       <c r="E27">
-        <v>-577.5999999999999</v>
+        <v>-557.8119999999999</v>
       </c>
       <c r="F27">
-        <v>494.7</v>
+        <v>514.4880000000001</v>
       </c>
       <c r="G27">
         <v>106.9</v>
@@ -3489,28 +3489,28 @@
         <v>174.175</v>
       </c>
       <c r="M27">
-        <v>26.86221</v>
+        <v>27.9366984</v>
       </c>
       <c r="N27">
-        <v>147.31279</v>
+        <v>146.2383016</v>
       </c>
       <c r="O27">
-        <v>29.462558</v>
+        <v>29.24766031999999</v>
       </c>
       <c r="P27">
-        <v>117.850232</v>
+        <v>116.99064128</v>
       </c>
       <c r="Q27">
-        <v>146.550232</v>
+        <v>145.69064128</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07554750627913294</v>
+        <v>0.07588602697647728</v>
       </c>
       <c r="T27">
-        <v>0.5642992017315159</v>
+        <v>0.5707208142690012</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.484016021019863</v>
+        <v>6.234630789442175</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06745005996259319</v>
+        <v>0.06759549021583666</v>
       </c>
       <c r="C28">
-        <v>1539.822276502443</v>
+        <v>1515.574439802486</v>
       </c>
       <c r="D28">
-        <v>1947.410276502443</v>
+        <v>1942.950439802486</v>
       </c>
       <c r="E28">
-        <v>-557.8119999999999</v>
+        <v>-538.0239999999999</v>
       </c>
       <c r="F28">
-        <v>514.4880000000001</v>
+        <v>534.2760000000001</v>
       </c>
       <c r="G28">
         <v>106.9</v>
@@ -3571,45 +3571,45 @@
         <v>174.175</v>
       </c>
       <c r="M28">
-        <v>27.9366984</v>
+        <v>29.54546280000001</v>
       </c>
       <c r="N28">
-        <v>146.2383016</v>
+        <v>144.6295372</v>
       </c>
       <c r="O28">
-        <v>29.24766031999999</v>
+        <v>28.92590744</v>
       </c>
       <c r="P28">
-        <v>116.99064128</v>
+        <v>115.70362976</v>
       </c>
       <c r="Q28">
-        <v>145.69064128</v>
+        <v>144.40362976</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07588602697647728</v>
+        <v>0.07623382221347487</v>
       </c>
       <c r="T28">
-        <v>0.5707208142690012</v>
+        <v>0.5773183613965546</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.234630789442175</v>
+        <v>5.895152199139015</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06759549021583666</v>
+        <v>0.06753292046908013</v>
       </c>
       <c r="C29">
-        <v>1515.574439802486</v>
+        <v>1497.702728699105</v>
       </c>
       <c r="D29">
-        <v>1942.950439802486</v>
+        <v>1944.866728699106</v>
       </c>
       <c r="E29">
-        <v>-538.0239999999999</v>
+        <v>-518.2359999999999</v>
       </c>
       <c r="F29">
-        <v>534.2760000000001</v>
+        <v>554.0640000000001</v>
       </c>
       <c r="G29">
         <v>106.9</v>
@@ -3653,28 +3653,28 @@
         <v>174.175</v>
       </c>
       <c r="M29">
-        <v>29.54546280000001</v>
+        <v>30.6397392</v>
       </c>
       <c r="N29">
-        <v>144.6295372</v>
+        <v>143.5352608</v>
       </c>
       <c r="O29">
-        <v>28.92590744</v>
+        <v>28.70705216</v>
       </c>
       <c r="P29">
-        <v>115.70362976</v>
+        <v>114.82820864</v>
       </c>
       <c r="Q29">
-        <v>144.40362976</v>
+        <v>143.52820864</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07623382221347487</v>
+        <v>0.07659127842927796</v>
       </c>
       <c r="T29">
-        <v>0.5773183613965546</v>
+        <v>0.5840991737220954</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.895152199139015</v>
+        <v>5.684611049169765</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06753292046908013</v>
+        <v>0.0674703507223236</v>
       </c>
       <c r="C30">
-        <v>1497.702728699105</v>
+        <v>1479.834801313939</v>
       </c>
       <c r="D30">
-        <v>1944.866728699106</v>
+        <v>1946.786801313939</v>
       </c>
       <c r="E30">
-        <v>-518.2359999999999</v>
+        <v>-498.4479999999999</v>
       </c>
       <c r="F30">
-        <v>554.0640000000001</v>
+        <v>573.8520000000001</v>
       </c>
       <c r="G30">
         <v>106.9</v>
@@ -3735,28 +3735,28 @@
         <v>174.175</v>
       </c>
       <c r="M30">
-        <v>30.6397392</v>
+        <v>31.73401560000001</v>
       </c>
       <c r="N30">
-        <v>143.5352608</v>
+        <v>142.4409844</v>
       </c>
       <c r="O30">
-        <v>28.70705216</v>
+        <v>28.48819688</v>
       </c>
       <c r="P30">
-        <v>114.82820864</v>
+        <v>113.95278752</v>
       </c>
       <c r="Q30">
-        <v>143.52820864</v>
+        <v>142.65278752</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07659127842927796</v>
+        <v>0.0769588038342586</v>
       </c>
       <c r="T30">
-        <v>0.5840991737220954</v>
+        <v>0.5910709948455389</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.684611049169765</v>
+        <v>5.488589978508738</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0674703507223236</v>
+        <v>0.06740778097556709</v>
       </c>
       <c r="C31">
-        <v>1479.834801313939</v>
+        <v>1461.970668864505</v>
       </c>
       <c r="D31">
-        <v>1946.786801313939</v>
+        <v>1948.710668864505</v>
       </c>
       <c r="E31">
-        <v>-498.448</v>
+        <v>-478.66</v>
       </c>
       <c r="F31">
-        <v>573.852</v>
+        <v>593.64</v>
       </c>
       <c r="G31">
         <v>106.9</v>
@@ -3817,28 +3817,28 @@
         <v>174.175</v>
       </c>
       <c r="M31">
-        <v>31.7340156</v>
+        <v>32.828292</v>
       </c>
       <c r="N31">
-        <v>142.4409844</v>
+        <v>141.346708</v>
       </c>
       <c r="O31">
-        <v>28.48819688</v>
+        <v>28.2693416</v>
       </c>
       <c r="P31">
-        <v>113.95278752</v>
+        <v>113.0773664</v>
       </c>
       <c r="Q31">
-        <v>142.65278752</v>
+        <v>141.7773664</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0769588038342586</v>
+        <v>0.07733682996509583</v>
       </c>
       <c r="T31">
-        <v>0.5910709948455389</v>
+        <v>0.5982420108582237</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.488589978508739</v>
+        <v>5.305636979225114</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06740778097556709</v>
+        <v>0.06734521122881054</v>
       </c>
       <c r="C32">
-        <v>1461.970668864505</v>
+        <v>1444.110342612709</v>
       </c>
       <c r="D32">
-        <v>1948.710668864505</v>
+        <v>1950.638342612709</v>
       </c>
       <c r="E32">
-        <v>-478.66</v>
+        <v>-458.872</v>
       </c>
       <c r="F32">
-        <v>593.64</v>
+        <v>613.428</v>
       </c>
       <c r="G32">
         <v>106.9</v>
@@ -3899,28 +3899,28 @@
         <v>174.175</v>
       </c>
       <c r="M32">
-        <v>32.828292</v>
+        <v>33.9225684</v>
       </c>
       <c r="N32">
-        <v>141.346708</v>
+        <v>140.2524316</v>
       </c>
       <c r="O32">
-        <v>28.2693416</v>
+        <v>28.05048631999999</v>
       </c>
       <c r="P32">
-        <v>113.0773664</v>
+        <v>112.20194528</v>
       </c>
       <c r="Q32">
-        <v>141.7773664</v>
+        <v>140.90194528</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07733682996509583</v>
+        <v>0.07772581337508776</v>
       </c>
       <c r="T32">
-        <v>0.5982420108582237</v>
+        <v>0.6056208824075079</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.305636979225114</v>
+        <v>5.134487399250109</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06734521122881054</v>
+        <v>0.06728264148205403</v>
       </c>
       <c r="C33">
-        <v>1444.110342612709</v>
+        <v>1426.253833865061</v>
       </c>
       <c r="D33">
-        <v>1950.638342612709</v>
+        <v>1952.569833865061</v>
       </c>
       <c r="E33">
-        <v>-458.872</v>
+        <v>-439.0839999999999</v>
       </c>
       <c r="F33">
-        <v>613.428</v>
+        <v>633.216</v>
       </c>
       <c r="G33">
         <v>106.9</v>
@@ -3981,28 +3981,28 @@
         <v>174.175</v>
       </c>
       <c r="M33">
-        <v>33.9225684</v>
+        <v>35.0168448</v>
       </c>
       <c r="N33">
-        <v>140.2524316</v>
+        <v>139.1581552</v>
       </c>
       <c r="O33">
-        <v>28.05048631999999</v>
+        <v>27.83163104</v>
       </c>
       <c r="P33">
-        <v>112.20194528</v>
+        <v>111.32652416</v>
       </c>
       <c r="Q33">
-        <v>140.90194528</v>
+        <v>140.02652416</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07772581337508776</v>
+        <v>0.07812623747360886</v>
       </c>
       <c r="T33">
-        <v>0.6056208824075079</v>
+        <v>0.6132167795905947</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.134487399250109</v>
+        <v>4.974034668023545</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06728264148205403</v>
+        <v>0.06722007173529751</v>
       </c>
       <c r="C34">
-        <v>1426.253833865061</v>
+        <v>1408.401153972897</v>
       </c>
       <c r="D34">
-        <v>1952.569833865061</v>
+        <v>1954.505153972897</v>
       </c>
       <c r="E34">
-        <v>-439.0839999999999</v>
+        <v>-419.2959999999999</v>
       </c>
       <c r="F34">
-        <v>633.216</v>
+        <v>653.004</v>
       </c>
       <c r="G34">
         <v>106.9</v>
@@ -4063,28 +4063,28 @@
         <v>174.175</v>
       </c>
       <c r="M34">
-        <v>35.0168448</v>
+        <v>36.1111212</v>
       </c>
       <c r="N34">
-        <v>139.1581552</v>
+        <v>138.0638788</v>
       </c>
       <c r="O34">
-        <v>27.83163104</v>
+        <v>27.61277576</v>
       </c>
       <c r="P34">
-        <v>111.32652416</v>
+        <v>110.45110304</v>
       </c>
       <c r="Q34">
-        <v>140.02652416</v>
+        <v>139.15110304</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07812623747360886</v>
+        <v>0.07853861453029479</v>
       </c>
       <c r="T34">
-        <v>0.6132167795905947</v>
+        <v>0.6210394199731767</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.974034668023545</v>
+        <v>4.823306344750105</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06722007173529751</v>
+        <v>0.06715750198854098</v>
       </c>
       <c r="C35">
-        <v>1408.401153972897</v>
+        <v>1390.552314332604</v>
       </c>
       <c r="D35">
-        <v>1954.505153972897</v>
+        <v>1956.444314332604</v>
       </c>
       <c r="E35">
-        <v>-419.2959999999999</v>
+        <v>-399.5079999999999</v>
       </c>
       <c r="F35">
-        <v>653.004</v>
+        <v>672.792</v>
       </c>
       <c r="G35">
         <v>106.9</v>
@@ -4145,28 +4145,28 @@
         <v>174.175</v>
       </c>
       <c r="M35">
-        <v>36.1111212</v>
+        <v>37.2053976</v>
       </c>
       <c r="N35">
-        <v>138.0638788</v>
+        <v>136.9696024</v>
       </c>
       <c r="O35">
-        <v>27.61277576</v>
+        <v>27.39392048</v>
       </c>
       <c r="P35">
-        <v>110.45110304</v>
+        <v>109.57568192</v>
       </c>
       <c r="Q35">
-        <v>139.15110304</v>
+        <v>138.27568192</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07853861453029479</v>
+        <v>0.07896348786142572</v>
       </c>
       <c r="T35">
-        <v>0.6210394199731767</v>
+        <v>0.6290991100643216</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.823306344750105</v>
+        <v>4.681444393433924</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06715750198854098</v>
+        <v>0.06709493224178445</v>
       </c>
       <c r="C36">
-        <v>1390.552314332604</v>
+        <v>1372.707326385839</v>
       </c>
       <c r="D36">
-        <v>1956.444314332604</v>
+        <v>1958.387326385839</v>
       </c>
       <c r="E36">
-        <v>-399.5079999999999</v>
+        <v>-379.7199999999999</v>
       </c>
       <c r="F36">
-        <v>672.792</v>
+        <v>692.58</v>
       </c>
       <c r="G36">
         <v>106.9</v>
@@ -4227,28 +4227,28 @@
         <v>174.175</v>
       </c>
       <c r="M36">
-        <v>37.2053976</v>
+        <v>38.299674</v>
       </c>
       <c r="N36">
-        <v>136.9696024</v>
+        <v>135.875326</v>
       </c>
       <c r="O36">
-        <v>27.39392048</v>
+        <v>27.1750652</v>
       </c>
       <c r="P36">
-        <v>109.57568192</v>
+        <v>108.7002608</v>
       </c>
       <c r="Q36">
-        <v>138.27568192</v>
+        <v>137.4002608</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07896348786142572</v>
+        <v>0.07940143421812992</v>
       </c>
       <c r="T36">
-        <v>0.6290991100643216</v>
+        <v>0.6374067906198095</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.681444393433924</v>
+        <v>4.547688839335811</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06709493224178445</v>
+        <v>0.06775236249502792</v>
       </c>
       <c r="C37">
-        <v>1372.707326385839</v>
+        <v>1332.694561028825</v>
       </c>
       <c r="D37">
-        <v>1958.387326385839</v>
+        <v>1938.162561028825</v>
       </c>
       <c r="E37">
-        <v>-379.7199999999999</v>
+        <v>-359.9319999999999</v>
       </c>
       <c r="F37">
-        <v>692.58</v>
+        <v>712.3680000000001</v>
       </c>
       <c r="G37">
         <v>106.9</v>
@@ -4309,45 +4309,45 @@
         <v>174.175</v>
       </c>
       <c r="M37">
-        <v>38.299674</v>
+        <v>41.1748704</v>
       </c>
       <c r="N37">
-        <v>135.875326</v>
+        <v>133.0001296</v>
       </c>
       <c r="O37">
-        <v>27.1750652</v>
+        <v>26.60002592</v>
       </c>
       <c r="P37">
-        <v>108.7002608</v>
+        <v>106.40010368</v>
       </c>
       <c r="Q37">
-        <v>137.4002608</v>
+        <v>135.10010368</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07940143421812992</v>
+        <v>0.07985306639848114</v>
       </c>
       <c r="T37">
-        <v>0.6374067906198095</v>
+        <v>0.6459740861926565</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.547688839335811</v>
+        <v>4.230128675766275</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06775236249502793</v>
+        <v>0.06770979274827141</v>
       </c>
       <c r="C38">
-        <v>1332.694561028825</v>
+        <v>1314.203492402925</v>
       </c>
       <c r="D38">
-        <v>1938.162561028824</v>
+        <v>1939.459492402925</v>
       </c>
       <c r="E38">
-        <v>-359.932</v>
+        <v>-340.144</v>
       </c>
       <c r="F38">
-        <v>712.3679999999999</v>
+        <v>732.1559999999999</v>
       </c>
       <c r="G38">
         <v>106.9</v>
@@ -4391,28 +4391,28 @@
         <v>174.175</v>
       </c>
       <c r="M38">
-        <v>41.1748704</v>
+        <v>42.3186168</v>
       </c>
       <c r="N38">
-        <v>133.0001296</v>
+        <v>131.8563832</v>
       </c>
       <c r="O38">
-        <v>26.60002592</v>
+        <v>26.37127664</v>
       </c>
       <c r="P38">
-        <v>106.40010368</v>
+        <v>105.48510656</v>
       </c>
       <c r="Q38">
-        <v>135.10010368</v>
+        <v>134.18510656</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07985306639848114</v>
+        <v>0.0803190361083673</v>
       </c>
       <c r="T38">
-        <v>0.6459740861926564</v>
+        <v>0.6548133594027366</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.230128675766275</v>
+        <v>4.115800873718538</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06770979274827141</v>
+        <v>0.06766722300151487</v>
       </c>
       <c r="C39">
-        <v>1314.203492402925</v>
+        <v>1295.714160635757</v>
       </c>
       <c r="D39">
-        <v>1939.459492402925</v>
+        <v>1940.758160635757</v>
       </c>
       <c r="E39">
-        <v>-340.144</v>
+        <v>-320.356</v>
       </c>
       <c r="F39">
-        <v>732.1559999999999</v>
+        <v>751.944</v>
       </c>
       <c r="G39">
         <v>106.9</v>
@@ -4473,28 +4473,28 @@
         <v>174.175</v>
       </c>
       <c r="M39">
-        <v>42.3186168</v>
+        <v>43.4623632</v>
       </c>
       <c r="N39">
-        <v>131.8563832</v>
+        <v>130.7126368</v>
       </c>
       <c r="O39">
-        <v>26.37127664</v>
+        <v>26.14252736</v>
       </c>
       <c r="P39">
-        <v>105.48510656</v>
+        <v>104.57010944</v>
       </c>
       <c r="Q39">
-        <v>134.18510656</v>
+        <v>133.27010944</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0803190361083673</v>
+        <v>0.08080003709921754</v>
       </c>
       <c r="T39">
-        <v>0.6548133594027366</v>
+        <v>0.663937770458303</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.115800873718538</v>
+        <v>4.007490324410155</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06766722300151487</v>
+        <v>0.06871665325475834</v>
       </c>
       <c r="C40">
-        <v>1295.714160635757</v>
+        <v>1244.410164809719</v>
       </c>
       <c r="D40">
-        <v>1940.758160635757</v>
+        <v>1909.242164809719</v>
       </c>
       <c r="E40">
-        <v>-320.356</v>
+        <v>-300.568</v>
       </c>
       <c r="F40">
-        <v>751.944</v>
+        <v>771.732</v>
       </c>
       <c r="G40">
         <v>106.9</v>
@@ -4555,45 +4555,45 @@
         <v>174.175</v>
       </c>
       <c r="M40">
-        <v>43.4623632</v>
+        <v>47.3071716</v>
       </c>
       <c r="N40">
-        <v>130.7126368</v>
+        <v>126.8678284</v>
       </c>
       <c r="O40">
-        <v>26.14252736</v>
+        <v>25.37356568</v>
       </c>
       <c r="P40">
-        <v>104.57010944</v>
+        <v>101.49426272</v>
       </c>
       <c r="Q40">
-        <v>133.27010944</v>
+        <v>130.19426272</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08080003709921754</v>
+        <v>0.08129680861435795</v>
       </c>
       <c r="T40">
-        <v>0.663937770458303</v>
+        <v>0.673361342532085</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.007490324410155</v>
+        <v>3.681788492297011</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06871665325475834</v>
+        <v>0.06870208350800183</v>
       </c>
       <c r="C41">
-        <v>1244.410164809719</v>
+        <v>1225.052708251206</v>
       </c>
       <c r="D41">
-        <v>1909.242164809719</v>
+        <v>1909.672708251206</v>
       </c>
       <c r="E41">
-        <v>-300.568</v>
+        <v>-280.78</v>
       </c>
       <c r="F41">
-        <v>771.732</v>
+        <v>791.52</v>
       </c>
       <c r="G41">
         <v>106.9</v>
@@ -4637,28 +4637,28 @@
         <v>174.175</v>
       </c>
       <c r="M41">
-        <v>47.3071716</v>
+        <v>48.520176</v>
       </c>
       <c r="N41">
-        <v>126.8678284</v>
+        <v>125.654824</v>
       </c>
       <c r="O41">
-        <v>25.37356568</v>
+        <v>25.1309648</v>
       </c>
       <c r="P41">
-        <v>101.49426272</v>
+        <v>100.5238592</v>
       </c>
       <c r="Q41">
-        <v>130.19426272</v>
+        <v>129.2238592</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08129680861435795</v>
+        <v>0.08181013918000304</v>
       </c>
       <c r="T41">
-        <v>0.673361342532085</v>
+        <v>0.683099033674993</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.681788492297011</v>
+        <v>3.589743779989586</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06870208350800183</v>
+        <v>0.06868751376124529</v>
       </c>
       <c r="C42">
-        <v>1225.052708251206</v>
+        <v>1205.695445915794</v>
       </c>
       <c r="D42">
-        <v>1909.672708251206</v>
+        <v>1910.103445915794</v>
       </c>
       <c r="E42">
-        <v>-280.78</v>
+        <v>-260.992</v>
       </c>
       <c r="F42">
-        <v>791.52</v>
+        <v>811.308</v>
       </c>
       <c r="G42">
         <v>106.9</v>
@@ -4719,28 +4719,28 @@
         <v>174.175</v>
       </c>
       <c r="M42">
-        <v>48.520176</v>
+        <v>49.7331804</v>
       </c>
       <c r="N42">
-        <v>125.654824</v>
+        <v>124.4418196</v>
       </c>
       <c r="O42">
-        <v>25.1309648</v>
+        <v>24.88836392</v>
       </c>
       <c r="P42">
-        <v>100.5238592</v>
+        <v>99.55345567999998</v>
       </c>
       <c r="Q42">
-        <v>129.2238592</v>
+        <v>128.25345568</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08181013918000304</v>
+        <v>0.08234087078177169</v>
       </c>
       <c r="T42">
-        <v>0.683099033674993</v>
+        <v>0.6931668160430843</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.589743779989586</v>
+        <v>3.502189053648376</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06868751376124529</v>
+        <v>0.06961374401448878</v>
       </c>
       <c r="C43">
-        <v>1205.695445915794</v>
+        <v>1158.905528638688</v>
       </c>
       <c r="D43">
-        <v>1910.103445915794</v>
+        <v>1883.101528638688</v>
       </c>
       <c r="E43">
-        <v>-260.992</v>
+        <v>-241.204</v>
       </c>
       <c r="F43">
-        <v>811.308</v>
+        <v>831.096</v>
       </c>
       <c r="G43">
         <v>106.9</v>
@@ -4801,45 +4801,45 @@
         <v>174.175</v>
       </c>
       <c r="M43">
-        <v>49.7331804</v>
+        <v>53.2732536</v>
       </c>
       <c r="N43">
-        <v>124.4418196</v>
+        <v>120.9017464</v>
       </c>
       <c r="O43">
-        <v>24.88836392</v>
+        <v>24.18034928</v>
       </c>
       <c r="P43">
-        <v>99.55345567999998</v>
+        <v>96.72139711999998</v>
       </c>
       <c r="Q43">
-        <v>128.25345568</v>
+        <v>125.42139712</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08234087078177169</v>
+        <v>0.0828899034732565</v>
       </c>
       <c r="T43">
-        <v>0.6931668160430843</v>
+        <v>0.7035817633204201</v>
       </c>
       <c r="U43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.502189053648376</v>
+        <v>3.269464285169922</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06961374401448878</v>
+        <v>0.06962157426773226</v>
       </c>
       <c r="C44">
-        <v>1158.905528638688</v>
+        <v>1138.892511085483</v>
       </c>
       <c r="D44">
-        <v>1883.101528638688</v>
+        <v>1882.876511085483</v>
       </c>
       <c r="E44">
-        <v>-241.204</v>
+        <v>-221.4159999999999</v>
       </c>
       <c r="F44">
-        <v>831.096</v>
+        <v>850.884</v>
       </c>
       <c r="G44">
         <v>106.9</v>
@@ -4883,28 +4883,28 @@
         <v>174.175</v>
       </c>
       <c r="M44">
-        <v>53.2732536</v>
+        <v>54.5416644</v>
       </c>
       <c r="N44">
-        <v>120.9017464</v>
+        <v>119.6333356</v>
       </c>
       <c r="O44">
-        <v>24.18034928</v>
+        <v>23.92666712</v>
       </c>
       <c r="P44">
-        <v>96.72139711999998</v>
+        <v>95.70666847999999</v>
       </c>
       <c r="Q44">
-        <v>125.42139712</v>
+        <v>124.40666848</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0828899034732565</v>
+        <v>0.0834582004697057</v>
       </c>
       <c r="T44">
-        <v>0.70358176332042</v>
+        <v>0.7143621473443291</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.269464285169922</v>
+        <v>3.193430232026436</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06962157426773226</v>
+        <v>0.06962940452097573</v>
       </c>
       <c r="C45">
-        <v>1138.892511085483</v>
+        <v>1118.879547301923</v>
       </c>
       <c r="D45">
-        <v>1882.876511085483</v>
+        <v>1882.651547301923</v>
       </c>
       <c r="E45">
-        <v>-221.4159999999999</v>
+        <v>-201.6279999999999</v>
       </c>
       <c r="F45">
-        <v>850.884</v>
+        <v>870.672</v>
       </c>
       <c r="G45">
         <v>106.9</v>
@@ -4965,28 +4965,28 @@
         <v>174.175</v>
       </c>
       <c r="M45">
-        <v>54.5416644</v>
+        <v>55.81007520000001</v>
       </c>
       <c r="N45">
-        <v>119.6333356</v>
+        <v>118.3649248</v>
       </c>
       <c r="O45">
-        <v>23.92666712</v>
+        <v>23.67298496</v>
       </c>
       <c r="P45">
-        <v>95.70666847999999</v>
+        <v>94.69193983999999</v>
       </c>
       <c r="Q45">
-        <v>124.40666848</v>
+        <v>123.39193984</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0834582004697057</v>
+        <v>0.08404679378745664</v>
       </c>
       <c r="T45">
-        <v>0.7143621473443291</v>
+        <v>0.7255275450833776</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.193430232026436</v>
+        <v>3.120852272207653</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06962940452097573</v>
+        <v>0.06963723477421919</v>
       </c>
       <c r="C46">
-        <v>1118.879547301923</v>
+        <v>1098.866637268738</v>
       </c>
       <c r="D46">
-        <v>1882.651547301923</v>
+        <v>1882.426637268738</v>
       </c>
       <c r="E46">
-        <v>-201.6279999999999</v>
+        <v>-181.8399999999999</v>
       </c>
       <c r="F46">
-        <v>870.672</v>
+        <v>890.46</v>
       </c>
       <c r="G46">
         <v>106.9</v>
@@ -5047,28 +5047,28 @@
         <v>174.175</v>
       </c>
       <c r="M46">
-        <v>55.81007520000001</v>
+        <v>57.07848600000001</v>
       </c>
       <c r="N46">
-        <v>118.3649248</v>
+        <v>117.096514</v>
       </c>
       <c r="O46">
-        <v>23.67298496</v>
+        <v>23.4193028</v>
       </c>
       <c r="P46">
-        <v>94.69193983999999</v>
+        <v>93.67721119999999</v>
       </c>
       <c r="Q46">
-        <v>123.39193984</v>
+        <v>122.3772112</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08404679378745664</v>
+        <v>0.08465679049858035</v>
       </c>
       <c r="T46">
-        <v>0.7255275450833776</v>
+        <v>0.7370989572856643</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.120852272207653</v>
+        <v>3.051499999491927</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06963723477421919</v>
+        <v>0.07251546502746267</v>
       </c>
       <c r="C47">
-        <v>1098.866637268738</v>
+        <v>999.8937044299698</v>
       </c>
       <c r="D47">
-        <v>1882.426637268738</v>
+        <v>1803.24170442997</v>
       </c>
       <c r="E47">
-        <v>-181.8399999999999</v>
+        <v>-162.0519999999999</v>
       </c>
       <c r="F47">
-        <v>890.46</v>
+        <v>910.248</v>
       </c>
       <c r="G47">
         <v>106.9</v>
@@ -5129,45 +5129,45 @@
         <v>174.175</v>
       </c>
       <c r="M47">
-        <v>57.07848600000001</v>
+        <v>65.44683120000001</v>
       </c>
       <c r="N47">
-        <v>117.096514</v>
+        <v>108.7281688</v>
       </c>
       <c r="O47">
-        <v>23.4193028</v>
+        <v>21.74563376</v>
       </c>
       <c r="P47">
-        <v>93.67721119999999</v>
+        <v>86.98253503999999</v>
       </c>
       <c r="Q47">
-        <v>122.3772112</v>
+        <v>115.68253504</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08465679049858035</v>
+        <v>0.08528937968048642</v>
       </c>
       <c r="T47">
-        <v>0.7370989572856643</v>
+        <v>0.749098940310258</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.051499999491927</v>
+        <v>2.661320598819152</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07251546502746267</v>
+        <v>0.07258569528070616</v>
       </c>
       <c r="C48">
-        <v>999.8937044299698</v>
+        <v>978.2567270476161</v>
       </c>
       <c r="D48">
-        <v>1803.24170442997</v>
+        <v>1801.392727047616</v>
       </c>
       <c r="E48">
-        <v>-162.0519999999999</v>
+        <v>-142.2639999999999</v>
       </c>
       <c r="F48">
-        <v>910.248</v>
+        <v>930.0360000000001</v>
       </c>
       <c r="G48">
         <v>106.9</v>
@@ -5211,28 +5211,28 @@
         <v>174.175</v>
       </c>
       <c r="M48">
-        <v>65.44683120000001</v>
+        <v>66.86958840000001</v>
       </c>
       <c r="N48">
-        <v>108.7281688</v>
+        <v>107.3054116</v>
       </c>
       <c r="O48">
-        <v>21.74563376</v>
+        <v>21.46108232</v>
       </c>
       <c r="P48">
-        <v>86.98253503999999</v>
+        <v>85.84432927999998</v>
       </c>
       <c r="Q48">
-        <v>115.68253504</v>
+        <v>114.54432928</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08528937968048642</v>
+        <v>0.08594584015227574</v>
       </c>
       <c r="T48">
-        <v>0.749098940310258</v>
+        <v>0.7615517528829495</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.661320598819152</v>
+        <v>2.604696756291085</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07258569528070616</v>
+        <v>0.07265592553394962</v>
       </c>
       <c r="C49">
-        <v>978.2567270476161</v>
+        <v>956.6235375274405</v>
       </c>
       <c r="D49">
-        <v>1801.392727047616</v>
+        <v>1799.54753752744</v>
       </c>
       <c r="E49">
-        <v>-142.2639999999999</v>
+        <v>-122.4759999999999</v>
       </c>
       <c r="F49">
-        <v>930.0360000000001</v>
+        <v>949.8240000000001</v>
       </c>
       <c r="G49">
         <v>106.9</v>
@@ -5293,28 +5293,28 @@
         <v>174.175</v>
       </c>
       <c r="M49">
-        <v>66.86958840000001</v>
+        <v>68.2923456</v>
       </c>
       <c r="N49">
-        <v>107.3054116</v>
+        <v>105.8826544</v>
       </c>
       <c r="O49">
-        <v>21.46108232</v>
+        <v>21.17653088</v>
       </c>
       <c r="P49">
-        <v>85.84432927999998</v>
+        <v>84.70612351999998</v>
       </c>
       <c r="Q49">
-        <v>114.54432928</v>
+        <v>113.40612352</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08594584015227574</v>
+        <v>0.08662754910374926</v>
       </c>
       <c r="T49">
-        <v>0.7615517528829495</v>
+        <v>0.7744835197853599</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.604696756291085</v>
+        <v>2.550432240535021</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07265592553394962</v>
+        <v>0.07425495578719309</v>
       </c>
       <c r="C50">
-        <v>956.6235375274406</v>
+        <v>895.8230557227818</v>
       </c>
       <c r="D50">
-        <v>1799.54753752744</v>
+        <v>1758.535055722782</v>
       </c>
       <c r="E50">
-        <v>-122.476</v>
+        <v>-102.688</v>
       </c>
       <c r="F50">
-        <v>949.824</v>
+        <v>969.612</v>
       </c>
       <c r="G50">
         <v>106.9</v>
@@ -5375,45 +5375,45 @@
         <v>174.175</v>
       </c>
       <c r="M50">
-        <v>68.2923456</v>
+        <v>73.49658960000001</v>
       </c>
       <c r="N50">
-        <v>105.8826544</v>
+        <v>100.6784104</v>
       </c>
       <c r="O50">
-        <v>21.17653088</v>
+        <v>20.13568208</v>
       </c>
       <c r="P50">
-        <v>84.70612351999998</v>
+        <v>80.54272831999998</v>
       </c>
       <c r="Q50">
-        <v>113.40612352</v>
+        <v>109.24272832</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08662754910374926</v>
+        <v>0.08733599173959429</v>
       </c>
       <c r="T50">
-        <v>0.7744835197853599</v>
+        <v>0.7879224148015903</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.550432240535021</v>
+        <v>2.369837851632778</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07425495578719309</v>
+        <v>0.07435638604043657</v>
       </c>
       <c r="C51">
-        <v>895.8230557227818</v>
+        <v>873.4964970733571</v>
       </c>
       <c r="D51">
-        <v>1758.535055722782</v>
+        <v>1755.996497073357</v>
       </c>
       <c r="E51">
-        <v>-102.688</v>
+        <v>-82.89999999999998</v>
       </c>
       <c r="F51">
-        <v>969.612</v>
+        <v>989.4</v>
       </c>
       <c r="G51">
         <v>106.9</v>
@@ -5457,28 +5457,28 @@
         <v>174.175</v>
       </c>
       <c r="M51">
-        <v>73.49658960000001</v>
+        <v>74.99652</v>
       </c>
       <c r="N51">
-        <v>100.6784104</v>
+        <v>99.17847999999998</v>
       </c>
       <c r="O51">
-        <v>20.13568208</v>
+        <v>19.835696</v>
       </c>
       <c r="P51">
-        <v>80.54272831999998</v>
+        <v>79.34278399999998</v>
       </c>
       <c r="Q51">
-        <v>109.24272832</v>
+        <v>108.042784</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08733599173959429</v>
+        <v>0.08807277208087314</v>
       </c>
       <c r="T51">
-        <v>0.7879224148015903</v>
+        <v>0.80189886561847</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.369837851632778</v>
+        <v>2.322441094600122</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07435638604043657</v>
+        <v>0.07445781629368005</v>
       </c>
       <c r="C52">
-        <v>873.4964970733571</v>
+        <v>851.1772570050117</v>
       </c>
       <c r="D52">
-        <v>1755.996497073357</v>
+        <v>1753.465257005012</v>
       </c>
       <c r="E52">
-        <v>-82.89999999999998</v>
+        <v>-63.11199999999997</v>
       </c>
       <c r="F52">
-        <v>989.4</v>
+        <v>1009.188</v>
       </c>
       <c r="G52">
         <v>106.9</v>
@@ -5539,28 +5539,28 @@
         <v>174.175</v>
       </c>
       <c r="M52">
-        <v>74.99652</v>
+        <v>76.4964504</v>
       </c>
       <c r="N52">
-        <v>99.17847999999998</v>
+        <v>97.67854959999998</v>
       </c>
       <c r="O52">
-        <v>19.835696</v>
+        <v>19.53570992</v>
       </c>
       <c r="P52">
-        <v>79.34278399999998</v>
+        <v>78.14283967999998</v>
       </c>
       <c r="Q52">
-        <v>108.042784</v>
+        <v>106.84283968</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08807277208087314</v>
+        <v>0.08883962508914295</v>
       </c>
       <c r="T52">
-        <v>0.80189886561847</v>
+        <v>0.8164457838156306</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.322441094600122</v>
+        <v>2.276903033921688</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07445781629368005</v>
+        <v>0.07455924654692352</v>
       </c>
       <c r="C53">
-        <v>851.1772570050117</v>
+        <v>828.8653039144585</v>
       </c>
       <c r="D53">
-        <v>1753.465257005012</v>
+        <v>1750.941303914459</v>
       </c>
       <c r="E53">
-        <v>-63.11199999999997</v>
+        <v>-43.32399999999984</v>
       </c>
       <c r="F53">
-        <v>1009.188</v>
+        <v>1028.976</v>
       </c>
       <c r="G53">
         <v>106.9</v>
@@ -5621,28 +5621,28 @@
         <v>174.175</v>
       </c>
       <c r="M53">
-        <v>76.4964504</v>
+        <v>77.99638080000001</v>
       </c>
       <c r="N53">
-        <v>97.67854959999998</v>
+        <v>96.17861919999997</v>
       </c>
       <c r="O53">
-        <v>19.53570992</v>
+        <v>19.23572384</v>
       </c>
       <c r="P53">
-        <v>78.14283967999998</v>
+        <v>76.94289535999998</v>
       </c>
       <c r="Q53">
-        <v>106.84283968</v>
+        <v>105.64289536</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08883962508914295</v>
+        <v>0.08963843030609064</v>
       </c>
       <c r="T53">
-        <v>0.8164457838156306</v>
+        <v>0.8315988236043392</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.276903033921688</v>
+        <v>2.233116437115502</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07455924654692352</v>
+        <v>0.074660676800167</v>
       </c>
       <c r="C54">
-        <v>828.8653039144585</v>
+        <v>806.5606063801085</v>
       </c>
       <c r="D54">
-        <v>1750.941303914459</v>
+        <v>1748.424606380109</v>
       </c>
       <c r="E54">
-        <v>-43.32399999999984</v>
+        <v>-23.53599999999983</v>
       </c>
       <c r="F54">
-        <v>1028.976</v>
+        <v>1048.764</v>
       </c>
       <c r="G54">
         <v>106.9</v>
@@ -5703,28 +5703,28 @@
         <v>174.175</v>
       </c>
       <c r="M54">
-        <v>77.99638080000001</v>
+        <v>79.49631120000002</v>
       </c>
       <c r="N54">
-        <v>96.17861919999997</v>
+        <v>94.67868879999996</v>
       </c>
       <c r="O54">
-        <v>19.23572384</v>
+        <v>18.93573775999999</v>
       </c>
       <c r="P54">
-        <v>76.94289535999998</v>
+        <v>75.74295103999997</v>
       </c>
       <c r="Q54">
-        <v>105.64289536</v>
+        <v>104.44295104</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08963843030609064</v>
+        <v>0.09047122723439785</v>
       </c>
       <c r="T54">
-        <v>0.8315988236043392</v>
+        <v>0.847396673596823</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.233116437115502</v>
+        <v>2.190982164717096</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.074660676800167</v>
+        <v>0.07476210705341046</v>
       </c>
       <c r="C55">
-        <v>806.5606063801085</v>
+        <v>784.2631331607688</v>
       </c>
       <c r="D55">
-        <v>1748.424606380109</v>
+        <v>1745.915133160769</v>
       </c>
       <c r="E55">
-        <v>-23.53599999999983</v>
+        <v>-3.74799999999982</v>
       </c>
       <c r="F55">
-        <v>1048.764</v>
+        <v>1068.552</v>
       </c>
       <c r="G55">
         <v>106.9</v>
@@ -5785,28 +5785,28 @@
         <v>174.175</v>
       </c>
       <c r="M55">
-        <v>79.49631120000002</v>
+        <v>80.99624160000002</v>
       </c>
       <c r="N55">
-        <v>94.67868879999996</v>
+        <v>93.17875839999996</v>
       </c>
       <c r="O55">
-        <v>18.93573775999999</v>
+        <v>18.63575167999999</v>
       </c>
       <c r="P55">
-        <v>75.74295103999997</v>
+        <v>74.54300671999997</v>
       </c>
       <c r="Q55">
-        <v>104.44295104</v>
+        <v>103.24300672</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09047122723439785</v>
+        <v>0.09134023272480535</v>
       </c>
       <c r="T55">
-        <v>0.847396673596823</v>
+        <v>0.8638813866324581</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.190982164717096</v>
+        <v>2.150408420926039</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07476210705341046</v>
+        <v>0.07486353730665395</v>
       </c>
       <c r="C56">
-        <v>784.2631331607688</v>
+        <v>761.9728531943465</v>
       </c>
       <c r="D56">
-        <v>1745.915133160769</v>
+        <v>1743.412853194347</v>
       </c>
       <c r="E56">
-        <v>-3.74799999999982</v>
+        <v>16.04000000000019</v>
       </c>
       <c r="F56">
-        <v>1068.552</v>
+        <v>1088.34</v>
       </c>
       <c r="G56">
         <v>106.9</v>
@@ -5867,28 +5867,28 @@
         <v>174.175</v>
       </c>
       <c r="M56">
-        <v>80.99624160000002</v>
+        <v>82.49617200000002</v>
       </c>
       <c r="N56">
-        <v>93.17875839999996</v>
+        <v>91.67882799999997</v>
       </c>
       <c r="O56">
-        <v>18.63575167999999</v>
+        <v>18.33576559999999</v>
       </c>
       <c r="P56">
-        <v>74.54300671999997</v>
+        <v>73.34306239999998</v>
       </c>
       <c r="Q56">
-        <v>103.24300672</v>
+        <v>102.0430624</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09134023272480535</v>
+        <v>0.0922478606814532</v>
       </c>
       <c r="T56">
-        <v>0.8638813866324581</v>
+        <v>0.8810987535807882</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.150408420926039</v>
+        <v>2.111310086000111</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07486353730665395</v>
+        <v>0.07496496755989743</v>
       </c>
       <c r="C57">
-        <v>761.9728531943465</v>
+        <v>739.6897355965707</v>
       </c>
       <c r="D57">
-        <v>1743.412853194347</v>
+        <v>1740.917735596571</v>
       </c>
       <c r="E57">
-        <v>16.04000000000019</v>
+        <v>35.8280000000002</v>
       </c>
       <c r="F57">
-        <v>1088.34</v>
+        <v>1108.128</v>
       </c>
       <c r="G57">
         <v>106.9</v>
@@ -5949,28 +5949,28 @@
         <v>174.175</v>
       </c>
       <c r="M57">
-        <v>82.49617200000002</v>
+        <v>83.99610240000001</v>
       </c>
       <c r="N57">
-        <v>91.67882799999997</v>
+        <v>90.17889759999997</v>
       </c>
       <c r="O57">
-        <v>18.33576559999999</v>
+        <v>18.03577951999999</v>
       </c>
       <c r="P57">
-        <v>73.34306239999998</v>
+        <v>72.14311807999998</v>
       </c>
       <c r="Q57">
-        <v>102.0430624</v>
+        <v>100.84311808</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.0922478606814532</v>
+        <v>0.09319674445431231</v>
       </c>
       <c r="T57">
-        <v>0.8810987535807882</v>
+        <v>0.8990987281176787</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.111310086000111</v>
+        <v>2.07360812017868</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07496496755989743</v>
+        <v>0.07506639781314089</v>
       </c>
       <c r="C58">
-        <v>739.6897355965707</v>
+        <v>717.41374965972</v>
       </c>
       <c r="D58">
-        <v>1740.917735596571</v>
+        <v>1738.42974965972</v>
       </c>
       <c r="E58">
-        <v>35.8280000000002</v>
+        <v>55.61600000000021</v>
       </c>
       <c r="F58">
-        <v>1108.128</v>
+        <v>1127.916</v>
       </c>
       <c r="G58">
         <v>106.9</v>
@@ -6031,28 +6031,28 @@
         <v>174.175</v>
       </c>
       <c r="M58">
-        <v>83.99610240000001</v>
+        <v>85.49603280000002</v>
       </c>
       <c r="N58">
-        <v>90.17889759999997</v>
+        <v>88.67896719999996</v>
       </c>
       <c r="O58">
-        <v>18.03577951999999</v>
+        <v>17.73579343999999</v>
       </c>
       <c r="P58">
-        <v>72.14311807999998</v>
+        <v>70.94317375999997</v>
       </c>
       <c r="Q58">
-        <v>100.84311808</v>
+        <v>99.64317375999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09319674445431231</v>
+        <v>0.0941897623561416</v>
       </c>
       <c r="T58">
-        <v>0.8990987281176787</v>
+        <v>0.917935910772564</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.07360812017868</v>
+        <v>2.037229030350984</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07506639781314089</v>
+        <v>0.07516782806638436</v>
       </c>
       <c r="C59">
-        <v>717.41374965972</v>
+        <v>695.1448648513622</v>
       </c>
       <c r="D59">
-        <v>1738.42974965972</v>
+        <v>1735.948864851362</v>
       </c>
       <c r="E59">
-        <v>55.61600000000021</v>
+        <v>75.40400000000022</v>
       </c>
       <c r="F59">
-        <v>1127.916</v>
+        <v>1147.704</v>
       </c>
       <c r="G59">
         <v>106.9</v>
@@ -6113,28 +6113,28 @@
         <v>174.175</v>
       </c>
       <c r="M59">
-        <v>85.49603280000002</v>
+        <v>86.99596320000002</v>
       </c>
       <c r="N59">
-        <v>88.67896719999996</v>
+        <v>87.17903679999996</v>
       </c>
       <c r="O59">
-        <v>17.73579343999999</v>
+        <v>17.43580735999999</v>
       </c>
       <c r="P59">
-        <v>70.94317375999997</v>
+        <v>69.74322943999996</v>
       </c>
       <c r="Q59">
-        <v>99.64317375999998</v>
+        <v>98.44322943999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.0941897623561416</v>
+        <v>0.09523006682472468</v>
       </c>
       <c r="T59">
-        <v>0.917935910772564</v>
+        <v>0.9376701021253011</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.037229030350984</v>
+        <v>2.002104391896657</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07516782806638436</v>
+        <v>0.08197165831962784</v>
       </c>
       <c r="C60">
-        <v>695.1448648513624</v>
+        <v>523.697268769952</v>
       </c>
       <c r="D60">
-        <v>1735.948864851362</v>
+        <v>1584.289268769952</v>
       </c>
       <c r="E60">
-        <v>75.404</v>
+        <v>95.19200000000001</v>
       </c>
       <c r="F60">
-        <v>1147.704</v>
+        <v>1167.492</v>
       </c>
       <c r="G60">
         <v>106.9</v>
@@ -6195,45 +6195,45 @@
         <v>174.175</v>
       </c>
       <c r="M60">
-        <v>86.99596320000001</v>
+        <v>105.07428</v>
       </c>
       <c r="N60">
-        <v>87.17903679999998</v>
+        <v>69.10072</v>
       </c>
       <c r="O60">
-        <v>17.43580735999999</v>
+        <v>13.820144</v>
       </c>
       <c r="P60">
-        <v>69.74322943999998</v>
+        <v>55.280576</v>
       </c>
       <c r="Q60">
-        <v>98.44322944</v>
+        <v>83.98057600000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09523006682472465</v>
+        <v>0.09632111785275083</v>
       </c>
       <c r="T60">
-        <v>0.9376701021253008</v>
+        <v>0.9583669369586594</v>
       </c>
       <c r="U60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.002104391896657</v>
+        <v>1.657636864130784</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08197165831962784</v>
+        <v>0.08218668857287131</v>
       </c>
       <c r="C61">
-        <v>523.697268769952</v>
+        <v>499.5469632963541</v>
       </c>
       <c r="D61">
-        <v>1584.289268769952</v>
+        <v>1579.926963296354</v>
       </c>
       <c r="E61">
-        <v>95.19200000000001</v>
+        <v>114.98</v>
       </c>
       <c r="F61">
-        <v>1167.492</v>
+        <v>1187.28</v>
       </c>
       <c r="G61">
         <v>106.9</v>
@@ -6277,28 +6277,28 @@
         <v>174.175</v>
       </c>
       <c r="M61">
-        <v>105.07428</v>
+        <v>106.8552</v>
       </c>
       <c r="N61">
-        <v>69.10072</v>
+        <v>67.31979999999999</v>
       </c>
       <c r="O61">
-        <v>13.820144</v>
+        <v>13.46396</v>
       </c>
       <c r="P61">
-        <v>55.280576</v>
+        <v>53.85583999999999</v>
       </c>
       <c r="Q61">
-        <v>83.98057600000001</v>
+        <v>82.55584</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09632111785275083</v>
+        <v>0.09746672143217827</v>
       </c>
       <c r="T61">
-        <v>0.9583669369586594</v>
+        <v>0.9800986135336857</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.657636864130784</v>
+        <v>1.630009583061938</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08218668857287131</v>
+        <v>0.08240171882611477</v>
       </c>
       <c r="C62">
-        <v>499.5469632963541</v>
+        <v>475.4206148808723</v>
       </c>
       <c r="D62">
-        <v>1579.926963296354</v>
+        <v>1575.588614880872</v>
       </c>
       <c r="E62">
-        <v>114.98</v>
+        <v>134.768</v>
       </c>
       <c r="F62">
-        <v>1187.28</v>
+        <v>1207.068</v>
       </c>
       <c r="G62">
         <v>106.9</v>
@@ -6359,28 +6359,28 @@
         <v>174.175</v>
       </c>
       <c r="M62">
-        <v>106.8552</v>
+        <v>108.63612</v>
       </c>
       <c r="N62">
-        <v>67.31979999999999</v>
+        <v>65.53887999999999</v>
       </c>
       <c r="O62">
-        <v>13.46396</v>
+        <v>13.107776</v>
       </c>
       <c r="P62">
-        <v>53.85583999999999</v>
+        <v>52.43110399999999</v>
       </c>
       <c r="Q62">
-        <v>82.55584</v>
+        <v>81.13110400000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09746672143217827</v>
+        <v>0.09867107391311483</v>
       </c>
       <c r="T62">
-        <v>0.9800986135336857</v>
+        <v>1.002944735061277</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.630009583061938</v>
+        <v>1.603288114487152</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08240171882611477</v>
+        <v>0.08261674907935826</v>
       </c>
       <c r="C63">
-        <v>475.4206148808723</v>
+        <v>451.3180267116504</v>
       </c>
       <c r="D63">
-        <v>1575.588614880872</v>
+        <v>1571.27402671165</v>
       </c>
       <c r="E63">
-        <v>134.768</v>
+        <v>154.556</v>
       </c>
       <c r="F63">
-        <v>1207.068</v>
+        <v>1226.856</v>
       </c>
       <c r="G63">
         <v>106.9</v>
@@ -6441,28 +6441,28 @@
         <v>174.175</v>
       </c>
       <c r="M63">
-        <v>108.63612</v>
+        <v>110.41704</v>
       </c>
       <c r="N63">
-        <v>65.53887999999999</v>
+        <v>63.75795999999998</v>
       </c>
       <c r="O63">
-        <v>13.107776</v>
+        <v>12.751592</v>
       </c>
       <c r="P63">
-        <v>52.43110399999999</v>
+        <v>51.00636799999999</v>
       </c>
       <c r="Q63">
-        <v>81.13110400000001</v>
+        <v>79.706368</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09867107391311483</v>
+        <v>0.09993881336673224</v>
       </c>
       <c r="T63">
-        <v>1.002944735061277</v>
+        <v>1.02699328403769</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.603288114487152</v>
+        <v>1.577428628769617</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08261674907935826</v>
+        <v>0.08283177933260172</v>
       </c>
       <c r="C64">
-        <v>451.3180267116504</v>
+        <v>427.2390041267436</v>
       </c>
       <c r="D64">
-        <v>1571.27402671165</v>
+        <v>1566.983004126743</v>
       </c>
       <c r="E64">
-        <v>154.556</v>
+        <v>174.3440000000001</v>
       </c>
       <c r="F64">
-        <v>1226.856</v>
+        <v>1246.644</v>
       </c>
       <c r="G64">
         <v>106.9</v>
@@ -6523,28 +6523,28 @@
         <v>174.175</v>
       </c>
       <c r="M64">
-        <v>110.41704</v>
+        <v>112.19796</v>
       </c>
       <c r="N64">
-        <v>63.75795999999998</v>
+        <v>61.97703999999999</v>
       </c>
       <c r="O64">
-        <v>12.751592</v>
+        <v>12.395408</v>
       </c>
       <c r="P64">
-        <v>51.00636799999999</v>
+        <v>49.58163199999999</v>
       </c>
       <c r="Q64">
-        <v>79.706368</v>
+        <v>78.281632</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09993881336673224</v>
+        <v>0.101275079277302</v>
       </c>
       <c r="T64">
-        <v>1.02699328403769</v>
+        <v>1.052341754580395</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.577428628769617</v>
+        <v>1.552390079106607</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08283177933260172</v>
+        <v>0.0830468095858452</v>
       </c>
       <c r="C65">
-        <v>427.2390041267436</v>
+        <v>403.1833545848369</v>
       </c>
       <c r="D65">
-        <v>1566.983004126743</v>
+        <v>1562.715354584837</v>
       </c>
       <c r="E65">
-        <v>174.3440000000001</v>
+        <v>194.1320000000001</v>
       </c>
       <c r="F65">
-        <v>1246.644</v>
+        <v>1266.432</v>
       </c>
       <c r="G65">
         <v>106.9</v>
@@ -6605,28 +6605,28 @@
         <v>174.175</v>
       </c>
       <c r="M65">
-        <v>112.19796</v>
+        <v>113.97888</v>
       </c>
       <c r="N65">
-        <v>61.97703999999999</v>
+        <v>60.19611999999998</v>
       </c>
       <c r="O65">
-        <v>12.395408</v>
+        <v>12.039224</v>
       </c>
       <c r="P65">
-        <v>49.58163199999999</v>
+        <v>48.15689599999998</v>
       </c>
       <c r="Q65">
-        <v>78.281632</v>
+        <v>76.85689600000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.101275079277302</v>
+        <v>0.1026855821829034</v>
       </c>
       <c r="T65">
-        <v>1.052341754580395</v>
+        <v>1.079098473486583</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.552390079106607</v>
+        <v>1.528133984120567</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0830468095858452</v>
+        <v>0.08326183983908868</v>
       </c>
       <c r="C66">
-        <v>403.1833545848369</v>
+        <v>379.150887636453</v>
       </c>
       <c r="D66">
-        <v>1562.715354584837</v>
+        <v>1558.470887636453</v>
       </c>
       <c r="E66">
-        <v>194.1320000000001</v>
+        <v>213.9200000000001</v>
       </c>
       <c r="F66">
-        <v>1266.432</v>
+        <v>1286.22</v>
       </c>
       <c r="G66">
         <v>106.9</v>
@@ -6687,28 +6687,28 @@
         <v>174.175</v>
       </c>
       <c r="M66">
-        <v>113.97888</v>
+        <v>115.7598</v>
       </c>
       <c r="N66">
-        <v>60.19611999999998</v>
+        <v>58.41519999999998</v>
       </c>
       <c r="O66">
-        <v>12.039224</v>
+        <v>11.68304</v>
       </c>
       <c r="P66">
-        <v>48.15689599999998</v>
+        <v>46.73215999999999</v>
       </c>
       <c r="Q66">
-        <v>76.85689600000001</v>
+        <v>75.43216000000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1026855821829034</v>
+        <v>0.1041766852545391</v>
       </c>
       <c r="T66">
-        <v>1.079098473486583</v>
+        <v>1.10738414775884</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.528133984120567</v>
+        <v>1.504624230518712</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08326183983908868</v>
+        <v>0.1155244882628935</v>
       </c>
       <c r="C67">
-        <v>379.150887636453</v>
+        <v>-91.85816185859881</v>
       </c>
       <c r="D67">
-        <v>1558.470887636453</v>
+        <v>1107.249838141401</v>
       </c>
       <c r="E67">
-        <v>213.9200000000001</v>
+        <v>233.7080000000001</v>
       </c>
       <c r="F67">
-        <v>1286.22</v>
+        <v>1306.008</v>
       </c>
       <c r="G67">
         <v>106.9</v>
@@ -6769,45 +6769,45 @@
         <v>174.175</v>
       </c>
       <c r="M67">
-        <v>115.7598</v>
+        <v>191.7219744</v>
       </c>
       <c r="N67">
-        <v>58.41519999999998</v>
+        <v>-17.54697440000004</v>
       </c>
       <c r="O67">
-        <v>11.68304</v>
+        <v>-3.509394880000008</v>
       </c>
       <c r="P67">
-        <v>46.73215999999999</v>
+        <v>-14.03757952000003</v>
       </c>
       <c r="Q67">
-        <v>75.43216000000001</v>
+        <v>14.66242047999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1041766852545391</v>
+        <v>0.1065899757645955</v>
       </c>
       <c r="T67">
-        <v>1.10738414775884</v>
+        <v>1.153163376968595</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2</v>
+        <v>0.1816953956843874</v>
       </c>
       <c r="W67">
-        <v>0.07199999999999999</v>
+        <v>0.1201271159135319</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.504624230518712</v>
+        <v>0.9084769784219371</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1155244882628935</v>
+        <v>0.1165344882628935</v>
       </c>
       <c r="C68">
-        <v>-91.85816185859881</v>
+        <v>-121.5919453186341</v>
       </c>
       <c r="D68">
-        <v>1107.249838141401</v>
+        <v>1097.304054681366</v>
       </c>
       <c r="E68">
-        <v>233.7080000000001</v>
+        <v>253.4960000000001</v>
       </c>
       <c r="F68">
-        <v>1306.008</v>
+        <v>1325.796</v>
       </c>
       <c r="G68">
         <v>106.9</v>
@@ -6851,37 +6851,37 @@
         <v>174.175</v>
       </c>
       <c r="M68">
-        <v>191.7219744</v>
+        <v>194.6268528</v>
       </c>
       <c r="N68">
-        <v>-17.54697440000004</v>
+        <v>-20.45185280000004</v>
       </c>
       <c r="O68">
-        <v>-3.509394880000008</v>
+        <v>-4.090370560000008</v>
       </c>
       <c r="P68">
-        <v>-14.03757952000003</v>
+        <v>-16.36148224000003</v>
       </c>
       <c r="Q68">
-        <v>14.66242047999999</v>
+        <v>12.33851775999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1065899757645955</v>
+        <v>0.1084320962423105</v>
       </c>
       <c r="T68">
-        <v>1.153163376968595</v>
+        <v>1.188107721725219</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1816953956843874</v>
+        <v>0.1789835241070085</v>
       </c>
       <c r="W68">
-        <v>0.1201271159135319</v>
+        <v>0.1205252186610912</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9084769784219371</v>
+        <v>0.8949176205350424</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1165344882628935</v>
+        <v>0.1175444882628935</v>
       </c>
       <c r="C69">
-        <v>-121.5919453186341</v>
+        <v>-151.1486450044024</v>
       </c>
       <c r="D69">
-        <v>1097.304054681366</v>
+        <v>1087.535354995598</v>
       </c>
       <c r="E69">
-        <v>253.4960000000001</v>
+        <v>273.2840000000001</v>
       </c>
       <c r="F69">
-        <v>1325.796</v>
+        <v>1345.584</v>
       </c>
       <c r="G69">
         <v>106.9</v>
@@ -6933,37 +6933,37 @@
         <v>174.175</v>
       </c>
       <c r="M69">
-        <v>194.6268528</v>
+        <v>197.5317312</v>
       </c>
       <c r="N69">
-        <v>-20.45185280000004</v>
+        <v>-23.35673120000004</v>
       </c>
       <c r="O69">
-        <v>-4.090370560000008</v>
+        <v>-4.671346240000008</v>
       </c>
       <c r="P69">
-        <v>-16.36148224000003</v>
+        <v>-18.68538496000003</v>
       </c>
       <c r="Q69">
-        <v>12.33851775999998</v>
+        <v>10.01461503999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1084320962423105</v>
+        <v>0.1103893492498827</v>
       </c>
       <c r="T69">
-        <v>1.188107721725219</v>
+        <v>1.225236088029132</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1789835241070085</v>
+        <v>0.176351413458376</v>
       </c>
       <c r="W69">
-        <v>0.1205252186610912</v>
+        <v>0.1209116125043104</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8949176205350424</v>
+        <v>0.8817570672918801</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1175444882628935</v>
+        <v>0.1185544882628935</v>
       </c>
       <c r="C70">
-        <v>-151.1486450044024</v>
+        <v>-180.5329486246467</v>
       </c>
       <c r="D70">
-        <v>1087.535354995598</v>
+        <v>1077.939051375353</v>
       </c>
       <c r="E70">
-        <v>273.2840000000001</v>
+        <v>293.0720000000001</v>
       </c>
       <c r="F70">
-        <v>1345.584</v>
+        <v>1365.372</v>
       </c>
       <c r="G70">
         <v>106.9</v>
@@ -7015,37 +7015,37 @@
         <v>174.175</v>
       </c>
       <c r="M70">
-        <v>197.5317312</v>
+        <v>200.4366096</v>
       </c>
       <c r="N70">
-        <v>-23.35673120000004</v>
+        <v>-26.26160960000004</v>
       </c>
       <c r="O70">
-        <v>-4.671346240000008</v>
+        <v>-5.252321920000009</v>
       </c>
       <c r="P70">
-        <v>-18.68538496000003</v>
+        <v>-21.00928768000004</v>
       </c>
       <c r="Q70">
-        <v>10.01461503999998</v>
+        <v>7.690712319999982</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1103893492498827</v>
+        <v>0.1124728766450402</v>
       </c>
       <c r="T70">
-        <v>1.225236088029132</v>
+        <v>1.264759832804265</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.176351413458376</v>
+        <v>0.1737955958720228</v>
       </c>
       <c r="W70">
-        <v>0.1209116125043104</v>
+        <v>0.1212868065259871</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8817570672918801</v>
+        <v>0.8689779793601137</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1185544882628935</v>
+        <v>0.1195644882628935</v>
       </c>
       <c r="C71">
-        <v>-180.5329486246467</v>
+        <v>-209.7493798798041</v>
       </c>
       <c r="D71">
-        <v>1077.939051375353</v>
+        <v>1068.510620120196</v>
       </c>
       <c r="E71">
-        <v>293.0720000000001</v>
+        <v>312.8600000000001</v>
       </c>
       <c r="F71">
-        <v>1365.372</v>
+        <v>1385.16</v>
       </c>
       <c r="G71">
         <v>106.9</v>
@@ -7097,37 +7097,37 @@
         <v>174.175</v>
       </c>
       <c r="M71">
-        <v>200.4366096</v>
+        <v>203.341488</v>
       </c>
       <c r="N71">
-        <v>-26.26160960000004</v>
+        <v>-29.16648800000004</v>
       </c>
       <c r="O71">
-        <v>-5.252321920000009</v>
+        <v>-5.833297600000009</v>
       </c>
       <c r="P71">
-        <v>-21.00928768000004</v>
+        <v>-23.33319040000003</v>
       </c>
       <c r="Q71">
-        <v>7.690712319999982</v>
+        <v>5.366809599999982</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1124728766450402</v>
+        <v>0.1146953058665415</v>
       </c>
       <c r="T71">
-        <v>1.264759832804265</v>
+        <v>1.306918493897741</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1737955958720228</v>
+        <v>0.1713128016452796</v>
       </c>
       <c r="W71">
-        <v>0.1212868065259871</v>
+        <v>0.121651280718473</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8689779793601137</v>
+        <v>0.8565640082263978</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1195644882628935</v>
+        <v>0.1205744882628935</v>
       </c>
       <c r="C72">
-        <v>-209.7493798798041</v>
+        <v>-238.8023055724843</v>
       </c>
       <c r="D72">
-        <v>1068.510620120196</v>
+        <v>1059.245694427516</v>
       </c>
       <c r="E72">
-        <v>312.8600000000001</v>
+        <v>332.6480000000001</v>
       </c>
       <c r="F72">
-        <v>1385.16</v>
+        <v>1404.948</v>
       </c>
       <c r="G72">
         <v>106.9</v>
@@ -7179,37 +7179,37 @@
         <v>174.175</v>
       </c>
       <c r="M72">
-        <v>203.341488</v>
+        <v>206.2463664</v>
       </c>
       <c r="N72">
-        <v>-29.16648800000004</v>
+        <v>-32.07136640000004</v>
       </c>
       <c r="O72">
-        <v>-5.833297600000009</v>
+        <v>-6.41427328000001</v>
       </c>
       <c r="P72">
-        <v>-23.33319040000003</v>
+        <v>-25.65709312000003</v>
       </c>
       <c r="Q72">
-        <v>5.366809599999982</v>
+        <v>3.042906879999983</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1146953058665415</v>
+        <v>0.1170710060688361</v>
       </c>
       <c r="T72">
-        <v>1.306918493897741</v>
+        <v>1.351984648859732</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1713128016452796</v>
+        <v>0.1688999452840785</v>
       </c>
       <c r="W72">
-        <v>0.121651280718473</v>
+        <v>0.1220054880322973</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8565640082263978</v>
+        <v>0.8444997264203922</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1205744882628935</v>
+        <v>0.1215844882628935</v>
       </c>
       <c r="C73">
-        <v>-238.8023055724841</v>
+        <v>-267.695942351208</v>
       </c>
       <c r="D73">
-        <v>1059.245694427516</v>
+        <v>1050.140057648792</v>
       </c>
       <c r="E73">
-        <v>332.6479999999999</v>
+        <v>352.4359999999999</v>
       </c>
       <c r="F73">
-        <v>1404.948</v>
+        <v>1424.736</v>
       </c>
       <c r="G73">
         <v>106.9</v>
@@ -7261,37 +7261,37 @@
         <v>174.175</v>
       </c>
       <c r="M73">
-        <v>206.2463664</v>
+        <v>209.1512448</v>
       </c>
       <c r="N73">
-        <v>-32.07136640000002</v>
+        <v>-34.97624480000002</v>
       </c>
       <c r="O73">
-        <v>-6.414273280000003</v>
+        <v>-6.995248960000004</v>
       </c>
       <c r="P73">
-        <v>-25.65709312000001</v>
+        <v>-27.98099584000001</v>
       </c>
       <c r="Q73">
-        <v>3.042906880000004</v>
+        <v>0.7190041600000043</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1170710060688361</v>
+        <v>0.119616399142723</v>
       </c>
       <c r="T73">
-        <v>1.351984648859731</v>
+        <v>1.400269814890436</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1688999452840785</v>
+        <v>0.1665541127106885</v>
       </c>
       <c r="W73">
-        <v>0.1220054880322973</v>
+        <v>0.122349856254071</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8444997264203923</v>
+        <v>0.8327705635534424</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1215844882628935</v>
+        <v>0.1225944882628935</v>
       </c>
       <c r="C74">
-        <v>-267.695942351208</v>
+        <v>-296.4343631092761</v>
       </c>
       <c r="D74">
-        <v>1050.140057648792</v>
+        <v>1041.189636890724</v>
       </c>
       <c r="E74">
-        <v>352.4359999999999</v>
+        <v>372.2239999999999</v>
       </c>
       <c r="F74">
-        <v>1424.736</v>
+        <v>1444.524</v>
       </c>
       <c r="G74">
         <v>106.9</v>
@@ -7343,37 +7343,37 @@
         <v>174.175</v>
       </c>
       <c r="M74">
-        <v>209.1512448</v>
+        <v>212.0561232</v>
       </c>
       <c r="N74">
-        <v>-34.97624480000002</v>
+        <v>-37.88112320000002</v>
       </c>
       <c r="O74">
-        <v>-6.995248960000004</v>
+        <v>-7.576224640000004</v>
       </c>
       <c r="P74">
-        <v>-27.98099584000001</v>
+        <v>-30.30489856000002</v>
       </c>
       <c r="Q74">
-        <v>0.7190041600000043</v>
+        <v>-1.604898559999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.119616399142723</v>
+        <v>0.1223503398517128</v>
       </c>
       <c r="T74">
-        <v>1.400269814890436</v>
+        <v>1.452131659886378</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1665541127106885</v>
+        <v>0.1642725495228708</v>
       </c>
       <c r="W74">
-        <v>0.122349856254071</v>
+        <v>0.1226847897300426</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8327705635534424</v>
+        <v>0.8213627476143541</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1225944882628935</v>
+        <v>0.1236044882628935</v>
       </c>
       <c r="C75">
-        <v>-296.4343631092761</v>
+        <v>-325.0215030591794</v>
       </c>
       <c r="D75">
-        <v>1041.189636890724</v>
+        <v>1032.39049694082</v>
       </c>
       <c r="E75">
-        <v>372.2239999999999</v>
+        <v>392.0119999999999</v>
       </c>
       <c r="F75">
-        <v>1444.524</v>
+        <v>1464.312</v>
       </c>
       <c r="G75">
         <v>106.9</v>
@@ -7425,37 +7425,37 @@
         <v>174.175</v>
       </c>
       <c r="M75">
-        <v>212.0561232</v>
+        <v>214.9610016</v>
       </c>
       <c r="N75">
-        <v>-37.88112320000002</v>
+        <v>-40.78600160000002</v>
       </c>
       <c r="O75">
-        <v>-7.576224640000004</v>
+        <v>-8.157200320000005</v>
       </c>
       <c r="P75">
-        <v>-30.30489856000002</v>
+        <v>-32.62880128000002</v>
       </c>
       <c r="Q75">
-        <v>-1.604898559999999</v>
+        <v>-3.928801280000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1223503398517128</v>
+        <v>0.1252945836921633</v>
       </c>
       <c r="T75">
-        <v>1.452131659886378</v>
+        <v>1.507982877574316</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1642725495228708</v>
+        <v>0.1620526502049942</v>
       </c>
       <c r="W75">
-        <v>0.1226847897300426</v>
+        <v>0.1230106709499069</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8213627476143541</v>
+        <v>0.810263251024971</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1236044882628935</v>
+        <v>0.165871854833552</v>
       </c>
       <c r="C76">
-        <v>-325.0215030591794</v>
+        <v>-614.5377616966543</v>
       </c>
       <c r="D76">
-        <v>1032.39049694082</v>
+        <v>762.6622383033456</v>
       </c>
       <c r="E76">
-        <v>392.0119999999999</v>
+        <v>411.8</v>
       </c>
       <c r="F76">
-        <v>1464.312</v>
+        <v>1484.1</v>
       </c>
       <c r="G76">
         <v>106.9</v>
@@ -7507,45 +7507,45 @@
         <v>174.175</v>
       </c>
       <c r="M76">
-        <v>214.9610016</v>
+        <v>298.00728</v>
       </c>
       <c r="N76">
-        <v>-40.78600160000002</v>
+        <v>-123.83228</v>
       </c>
       <c r="O76">
-        <v>-8.157200320000005</v>
+        <v>-24.766456</v>
       </c>
       <c r="P76">
-        <v>-32.62880128000002</v>
+        <v>-99.06582399999999</v>
       </c>
       <c r="Q76">
-        <v>-3.928801280000002</v>
+        <v>-70.36582399999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1252945836921633</v>
+        <v>0.1315038333224837</v>
       </c>
       <c r="T76">
-        <v>1.507982877574316</v>
+        <v>1.625770048601805</v>
       </c>
       <c r="U76">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1620526502049942</v>
+        <v>0.1168931175104179</v>
       </c>
       <c r="W76">
-        <v>0.1230106709499069</v>
+        <v>0.1773278620039081</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.810263251024971</v>
+        <v>0.5844655875520893</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.165871854833552</v>
+        <v>0.167421854833552</v>
       </c>
       <c r="C77">
-        <v>-614.5377616966543</v>
+        <v>-641.5634529178047</v>
       </c>
       <c r="D77">
-        <v>762.6622383033456</v>
+        <v>755.4245470821952</v>
       </c>
       <c r="E77">
-        <v>411.8</v>
+        <v>431.588</v>
       </c>
       <c r="F77">
-        <v>1484.1</v>
+        <v>1503.888</v>
       </c>
       <c r="G77">
         <v>106.9</v>
@@ -7589,37 +7589,37 @@
         <v>174.175</v>
       </c>
       <c r="M77">
-        <v>298.00728</v>
+        <v>301.9807104</v>
       </c>
       <c r="N77">
-        <v>-123.83228</v>
+        <v>-127.8057104</v>
       </c>
       <c r="O77">
-        <v>-24.766456</v>
+        <v>-25.56114208000001</v>
       </c>
       <c r="P77">
-        <v>-99.06582399999999</v>
+        <v>-102.24456832</v>
       </c>
       <c r="Q77">
-        <v>-70.36582399999998</v>
+        <v>-73.54456832000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1315038333224837</v>
+        <v>0.1350748263775872</v>
       </c>
       <c r="T77">
-        <v>1.625770048601805</v>
+        <v>1.693510467293547</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1168931175104179</v>
+        <v>0.1153550501747544</v>
       </c>
       <c r="W77">
-        <v>0.1773278620039081</v>
+        <v>0.1776367059249093</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5844655875520893</v>
+        <v>0.5767752508737722</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.167421854833552</v>
+        <v>0.168971854833552</v>
       </c>
       <c r="C78">
-        <v>-641.5634529178047</v>
+        <v>-668.4530636635483</v>
       </c>
       <c r="D78">
-        <v>755.4245470821952</v>
+        <v>748.3229363364517</v>
       </c>
       <c r="E78">
-        <v>431.588</v>
+        <v>451.376</v>
       </c>
       <c r="F78">
-        <v>1503.888</v>
+        <v>1523.676</v>
       </c>
       <c r="G78">
         <v>106.9</v>
@@ -7671,37 +7671,37 @@
         <v>174.175</v>
       </c>
       <c r="M78">
-        <v>301.9807104</v>
+        <v>305.9541408</v>
       </c>
       <c r="N78">
-        <v>-127.8057104</v>
+        <v>-131.7791408</v>
       </c>
       <c r="O78">
-        <v>-25.56114208000001</v>
+        <v>-26.35582816000001</v>
       </c>
       <c r="P78">
-        <v>-102.24456832</v>
+        <v>-105.42331264</v>
       </c>
       <c r="Q78">
-        <v>-73.54456832000001</v>
+        <v>-76.72331264</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1350748263775872</v>
+        <v>0.1389563405679171</v>
       </c>
       <c r="T78">
-        <v>1.693510467293547</v>
+        <v>1.767141357175875</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1153550501747544</v>
+        <v>0.1138569326400174</v>
       </c>
       <c r="W78">
-        <v>0.1776367059249093</v>
+        <v>0.1779375279258845</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5767752508737722</v>
+        <v>0.569284663200087</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.168971854833552</v>
+        <v>0.170521854833552</v>
       </c>
       <c r="C79">
-        <v>-668.4530636635483</v>
+        <v>-695.2103959958463</v>
       </c>
       <c r="D79">
-        <v>748.3229363364517</v>
+        <v>741.3536040041537</v>
       </c>
       <c r="E79">
-        <v>451.376</v>
+        <v>471.164</v>
       </c>
       <c r="F79">
-        <v>1523.676</v>
+        <v>1543.464</v>
       </c>
       <c r="G79">
         <v>106.9</v>
@@ -7753,37 +7753,37 @@
         <v>174.175</v>
       </c>
       <c r="M79">
-        <v>305.9541408</v>
+        <v>309.9275712</v>
       </c>
       <c r="N79">
-        <v>-131.7791408</v>
+        <v>-135.7525712</v>
       </c>
       <c r="O79">
-        <v>-26.35582816000001</v>
+        <v>-27.15051424</v>
       </c>
       <c r="P79">
-        <v>-105.42331264</v>
+        <v>-108.60205696</v>
       </c>
       <c r="Q79">
-        <v>-76.72331264</v>
+        <v>-79.90205695999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1389563405679171</v>
+        <v>0.1431907196846406</v>
       </c>
       <c r="T79">
-        <v>1.767141357175875</v>
+        <v>1.847465964320232</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1138569326400174</v>
+        <v>0.1123972283754018</v>
       </c>
       <c r="W79">
-        <v>0.1779375279258845</v>
+        <v>0.1782306365422193</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.569284663200087</v>
+        <v>0.5619861418770089</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.170521854833552</v>
+        <v>0.172071854833552</v>
       </c>
       <c r="C80">
-        <v>-695.2103959958463</v>
+        <v>-721.8391116451121</v>
       </c>
       <c r="D80">
-        <v>741.3536040041537</v>
+        <v>734.5128883548879</v>
       </c>
       <c r="E80">
-        <v>471.164</v>
+        <v>490.952</v>
       </c>
       <c r="F80">
-        <v>1543.464</v>
+        <v>1563.252</v>
       </c>
       <c r="G80">
         <v>106.9</v>
@@ -7835,37 +7835,37 @@
         <v>174.175</v>
       </c>
       <c r="M80">
-        <v>309.9275712</v>
+        <v>313.9010016</v>
       </c>
       <c r="N80">
-        <v>-135.7525712</v>
+        <v>-139.7260016</v>
       </c>
       <c r="O80">
-        <v>-27.15051424</v>
+        <v>-27.94520032</v>
       </c>
       <c r="P80">
-        <v>-108.60205696</v>
+        <v>-111.78080128</v>
       </c>
       <c r="Q80">
-        <v>-79.90205695999998</v>
+        <v>-83.08080127999997</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1431907196846406</v>
+        <v>0.1478283730029568</v>
       </c>
       <c r="T80">
-        <v>1.847465964320232</v>
+        <v>1.935440534049767</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1123972283754018</v>
+        <v>0.1109744786491309</v>
       </c>
       <c r="W80">
-        <v>0.1782306365422193</v>
+        <v>0.1785163246872545</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5619861418770089</v>
+        <v>0.5548723932456544</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.172071854833552</v>
+        <v>0.173621854833552</v>
       </c>
       <c r="C81">
-        <v>-721.8391116451121</v>
+        <v>-748.3427384254441</v>
       </c>
       <c r="D81">
-        <v>734.5128883548879</v>
+        <v>727.7972615745559</v>
       </c>
       <c r="E81">
-        <v>490.952</v>
+        <v>510.74</v>
       </c>
       <c r="F81">
-        <v>1563.252</v>
+        <v>1583.04</v>
       </c>
       <c r="G81">
         <v>106.9</v>
@@ -7917,37 +7917,37 @@
         <v>174.175</v>
       </c>
       <c r="M81">
-        <v>313.9010016</v>
+        <v>317.874432</v>
       </c>
       <c r="N81">
-        <v>-139.7260016</v>
+        <v>-143.699432</v>
       </c>
       <c r="O81">
-        <v>-27.94520032</v>
+        <v>-28.73988640000001</v>
       </c>
       <c r="P81">
-        <v>-111.78080128</v>
+        <v>-114.9595456</v>
       </c>
       <c r="Q81">
-        <v>-83.08080127999997</v>
+        <v>-86.25954560000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1478283730029568</v>
+        <v>0.1529297916531047</v>
       </c>
       <c r="T81">
-        <v>1.935440534049767</v>
+        <v>2.032212560752256</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1109744786491309</v>
+        <v>0.1095872976660167</v>
       </c>
       <c r="W81">
-        <v>0.1785163246872545</v>
+        <v>0.1787948706286638</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5548723932456544</v>
+        <v>0.5479364883300837</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.173621854833552</v>
+        <v>0.175171854833552</v>
       </c>
       <c r="C82">
-        <v>-748.3427384254441</v>
+        <v>-774.7246763011216</v>
       </c>
       <c r="D82">
-        <v>727.7972615745559</v>
+        <v>721.2033236988784</v>
       </c>
       <c r="E82">
-        <v>510.74</v>
+        <v>530.528</v>
       </c>
       <c r="F82">
-        <v>1583.04</v>
+        <v>1602.828</v>
       </c>
       <c r="G82">
         <v>106.9</v>
@@ -7999,37 +7999,37 @@
         <v>174.175</v>
       </c>
       <c r="M82">
-        <v>317.874432</v>
+        <v>321.8478624</v>
       </c>
       <c r="N82">
-        <v>-143.699432</v>
+        <v>-147.6728624</v>
       </c>
       <c r="O82">
-        <v>-28.73988640000001</v>
+        <v>-29.53457248</v>
       </c>
       <c r="P82">
-        <v>-114.9595456</v>
+        <v>-118.13828992</v>
       </c>
       <c r="Q82">
-        <v>-86.25954560000001</v>
+        <v>-89.43828991999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1529297916531047</v>
+        <v>0.1585682017401102</v>
       </c>
       <c r="T82">
-        <v>2.032212560752256</v>
+        <v>2.139171116581323</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1095872976660167</v>
+        <v>0.1082343680652017</v>
       </c>
       <c r="W82">
-        <v>0.1787948706286638</v>
+        <v>0.1790665388925075</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5479364883300837</v>
+        <v>0.5411718403260086</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.175171854833552</v>
+        <v>0.176721854833552</v>
       </c>
       <c r="C83">
-        <v>-774.7246763011216</v>
+        <v>-800.9882031262832</v>
       </c>
       <c r="D83">
-        <v>721.2033236988784</v>
+        <v>714.7277968737168</v>
       </c>
       <c r="E83">
-        <v>530.528</v>
+        <v>550.316</v>
       </c>
       <c r="F83">
-        <v>1602.828</v>
+        <v>1622.616</v>
       </c>
       <c r="G83">
         <v>106.9</v>
@@ -8081,37 +8081,37 @@
         <v>174.175</v>
       </c>
       <c r="M83">
-        <v>321.8478624</v>
+        <v>325.8212928</v>
       </c>
       <c r="N83">
-        <v>-147.6728624</v>
+        <v>-151.6462928</v>
       </c>
       <c r="O83">
-        <v>-29.53457248</v>
+        <v>-30.32925856</v>
       </c>
       <c r="P83">
-        <v>-118.13828992</v>
+        <v>-121.31703424</v>
       </c>
       <c r="Q83">
-        <v>-89.43828991999999</v>
+        <v>-92.61703423999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1585682017401102</v>
+        <v>0.164833101836783</v>
       </c>
       <c r="T83">
-        <v>2.139171116581323</v>
+        <v>2.258013956391396</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1082343680652017</v>
+        <v>0.1069144367473334</v>
       </c>
       <c r="W83">
-        <v>0.1790665388925075</v>
+        <v>0.1793315811011355</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5411718403260086</v>
+        <v>0.534572183736667</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.176721854833552</v>
+        <v>0.178271854833552</v>
       </c>
       <c r="C84">
-        <v>-800.9882031262832</v>
+        <v>-827.1364800781437</v>
       </c>
       <c r="D84">
-        <v>714.7277968737168</v>
+        <v>708.3675199218563</v>
       </c>
       <c r="E84">
-        <v>550.316</v>
+        <v>570.104</v>
       </c>
       <c r="F84">
-        <v>1622.616</v>
+        <v>1642.404</v>
       </c>
       <c r="G84">
         <v>106.9</v>
@@ -8163,37 +8163,37 @@
         <v>174.175</v>
       </c>
       <c r="M84">
-        <v>325.8212928</v>
+        <v>329.7947232</v>
       </c>
       <c r="N84">
-        <v>-151.6462928</v>
+        <v>-155.6197232</v>
       </c>
       <c r="O84">
-        <v>-30.32925856</v>
+        <v>-31.12394464000001</v>
       </c>
       <c r="P84">
-        <v>-121.31703424</v>
+        <v>-124.49577856</v>
       </c>
       <c r="Q84">
-        <v>-92.61703423999998</v>
+        <v>-95.79577856000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.164833101836783</v>
+        <v>0.1718350490036526</v>
       </c>
       <c r="T84">
-        <v>2.258013956391396</v>
+        <v>2.390838306767361</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1069144367473334</v>
+        <v>0.1056263110033896</v>
       </c>
       <c r="W84">
-        <v>0.1793315811011355</v>
+        <v>0.1795902367505194</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.534572183736667</v>
+        <v>0.5281315550169481</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.178271854833552</v>
+        <v>0.179821854833552</v>
       </c>
       <c r="C85">
-        <v>-827.1364800781437</v>
+        <v>-853.1725568026732</v>
       </c>
       <c r="D85">
-        <v>708.3675199218563</v>
+        <v>702.1194431973269</v>
       </c>
       <c r="E85">
-        <v>570.104</v>
+        <v>589.8920000000001</v>
       </c>
       <c r="F85">
-        <v>1642.404</v>
+        <v>1662.192</v>
       </c>
       <c r="G85">
         <v>106.9</v>
@@ -8245,37 +8245,37 @@
         <v>174.175</v>
       </c>
       <c r="M85">
-        <v>329.7947232</v>
+        <v>333.7681536</v>
       </c>
       <c r="N85">
-        <v>-155.6197232</v>
+        <v>-159.5931536</v>
       </c>
       <c r="O85">
-        <v>-31.12394464000001</v>
+        <v>-31.91863072000001</v>
       </c>
       <c r="P85">
-        <v>-124.49577856</v>
+        <v>-127.67452288</v>
       </c>
       <c r="Q85">
-        <v>-95.79577856000002</v>
+        <v>-98.97452287999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1718350490036526</v>
+        <v>0.1797122395663809</v>
       </c>
       <c r="T85">
-        <v>2.390838306767361</v>
+        <v>2.540265700940321</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1056263110033896</v>
+        <v>0.1043688549200159</v>
       </c>
       <c r="W85">
-        <v>0.1795902367505194</v>
+        <v>0.1798427339320608</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5281315550169481</v>
+        <v>0.5218442746000798</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.179821854833552</v>
+        <v>0.181371854833552</v>
       </c>
       <c r="C86">
-        <v>-853.1725568026732</v>
+        <v>-879.0993762903364</v>
       </c>
       <c r="D86">
-        <v>702.1194431973269</v>
+        <v>695.9806237096636</v>
       </c>
       <c r="E86">
-        <v>589.8920000000001</v>
+        <v>609.6800000000001</v>
       </c>
       <c r="F86">
-        <v>1662.192</v>
+        <v>1681.98</v>
       </c>
       <c r="G86">
         <v>106.9</v>
@@ -8327,37 +8327,37 @@
         <v>174.175</v>
       </c>
       <c r="M86">
-        <v>333.7681536</v>
+        <v>337.741584</v>
       </c>
       <c r="N86">
-        <v>-159.5931536</v>
+        <v>-163.566584</v>
       </c>
       <c r="O86">
-        <v>-31.91863072000001</v>
+        <v>-32.7133168</v>
       </c>
       <c r="P86">
-        <v>-127.67452288</v>
+        <v>-130.8532672</v>
       </c>
       <c r="Q86">
-        <v>-98.97452287999999</v>
+        <v>-102.1532672</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1797122395663808</v>
+        <v>0.1886397222041395</v>
       </c>
       <c r="T86">
-        <v>2.540265700940319</v>
+        <v>2.709616747669674</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1043688549200159</v>
+        <v>0.103140986038604</v>
       </c>
       <c r="W86">
-        <v>0.1798427339320608</v>
+        <v>0.1800892900034483</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5218442746000798</v>
+        <v>0.5157049301930199</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.181371854833552</v>
+        <v>0.182921854833552</v>
       </c>
       <c r="C87">
-        <v>-879.0993762903364</v>
+        <v>-904.919779498268</v>
       </c>
       <c r="D87">
-        <v>695.9806237096636</v>
+        <v>689.9482205017321</v>
       </c>
       <c r="E87">
-        <v>609.6800000000001</v>
+        <v>629.4680000000001</v>
       </c>
       <c r="F87">
-        <v>1681.98</v>
+        <v>1701.768</v>
       </c>
       <c r="G87">
         <v>106.9</v>
@@ -8409,37 +8409,37 @@
         <v>174.175</v>
       </c>
       <c r="M87">
-        <v>337.741584</v>
+        <v>341.7150144</v>
       </c>
       <c r="N87">
-        <v>-163.566584</v>
+        <v>-167.5400144</v>
       </c>
       <c r="O87">
-        <v>-32.7133168</v>
+        <v>-33.50800288000001</v>
       </c>
       <c r="P87">
-        <v>-130.8532672</v>
+        <v>-134.03201152</v>
       </c>
       <c r="Q87">
-        <v>-102.1532672</v>
+        <v>-105.33201152</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1886397222041395</v>
+        <v>0.1988425595044352</v>
       </c>
       <c r="T87">
-        <v>2.709616747669674</v>
+        <v>2.903160801074651</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.103140986038604</v>
+        <v>0.1019416722474574</v>
       </c>
       <c r="W87">
-        <v>0.1800892900034483</v>
+        <v>0.1803301122127106</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5157049301930199</v>
+        <v>0.5097083612372871</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.182921854833552</v>
+        <v>0.184471854833552</v>
       </c>
       <c r="C88">
-        <v>-904.919779498268</v>
+        <v>-930.6365097341386</v>
       </c>
       <c r="D88">
-        <v>689.9482205017321</v>
+        <v>684.0194902658615</v>
       </c>
       <c r="E88">
-        <v>629.4680000000001</v>
+        <v>649.2560000000001</v>
       </c>
       <c r="F88">
-        <v>1701.768</v>
+        <v>1721.556</v>
       </c>
       <c r="G88">
         <v>106.9</v>
@@ -8491,37 +8491,37 @@
         <v>174.175</v>
       </c>
       <c r="M88">
-        <v>341.7150144</v>
+        <v>345.6884448</v>
       </c>
       <c r="N88">
-        <v>-167.5400144</v>
+        <v>-171.5134448</v>
       </c>
       <c r="O88">
-        <v>-33.50800288000001</v>
+        <v>-34.30268896</v>
       </c>
       <c r="P88">
-        <v>-134.03201152</v>
+        <v>-137.21075584</v>
       </c>
       <c r="Q88">
-        <v>-105.33201152</v>
+        <v>-108.51075584</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1988425595044352</v>
+        <v>0.2106150640816994</v>
       </c>
       <c r="T88">
-        <v>2.903160801074651</v>
+        <v>3.126480862695778</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1019416722474574</v>
+        <v>0.1007699288882913</v>
       </c>
       <c r="W88">
-        <v>0.1803301122127106</v>
+        <v>0.1805653982792311</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5097083612372871</v>
+        <v>0.5038496444414562</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.184471854833552</v>
+        <v>0.2171274613927864</v>
       </c>
       <c r="C89">
-        <v>-930.6365097341386</v>
+        <v>-1055.276245027221</v>
       </c>
       <c r="D89">
-        <v>684.0194902658615</v>
+        <v>579.1677549727794</v>
       </c>
       <c r="E89">
-        <v>649.2560000000001</v>
+        <v>669.0440000000001</v>
       </c>
       <c r="F89">
-        <v>1721.556</v>
+        <v>1741.344</v>
       </c>
       <c r="G89">
         <v>106.9</v>
@@ -8573,45 +8573,45 @@
         <v>174.175</v>
       </c>
       <c r="M89">
-        <v>345.6884448</v>
+        <v>410.6089152</v>
       </c>
       <c r="N89">
-        <v>-171.5134448</v>
+        <v>-236.4339152</v>
       </c>
       <c r="O89">
-        <v>-34.30268896</v>
+        <v>-47.28678304000001</v>
       </c>
       <c r="P89">
-        <v>-137.21075584</v>
+        <v>-189.14713216</v>
       </c>
       <c r="Q89">
-        <v>-108.51075584</v>
+        <v>-160.44713216</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2106150640816994</v>
+        <v>0.2268963740821276</v>
       </c>
       <c r="T89">
-        <v>3.126480862695778</v>
+        <v>3.435331297087643</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1007699288882913</v>
+        <v>0.08483741757782466</v>
       </c>
       <c r="W89">
-        <v>0.1805653982792311</v>
+        <v>0.2157953369351489</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5038496444414562</v>
+        <v>0.4241870878891233</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2171274613927864</v>
+        <v>0.2190274613927864</v>
       </c>
       <c r="C90">
-        <v>-1055.276245027221</v>
+        <v>-1080.184023644185</v>
       </c>
       <c r="D90">
-        <v>579.1677549727794</v>
+        <v>574.0479763558153</v>
       </c>
       <c r="E90">
-        <v>669.0440000000001</v>
+        <v>688.8320000000001</v>
       </c>
       <c r="F90">
-        <v>1741.344</v>
+        <v>1761.132</v>
       </c>
       <c r="G90">
         <v>106.9</v>
@@ -8655,37 +8655,37 @@
         <v>174.175</v>
       </c>
       <c r="M90">
-        <v>410.6089152</v>
+        <v>415.2749256</v>
       </c>
       <c r="N90">
-        <v>-236.4339152</v>
+        <v>-241.0999256</v>
       </c>
       <c r="O90">
-        <v>-47.28678304000001</v>
+        <v>-48.21998512000001</v>
       </c>
       <c r="P90">
-        <v>-189.14713216</v>
+        <v>-192.87994048</v>
       </c>
       <c r="Q90">
-        <v>-160.44713216</v>
+        <v>-164.17994048</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2268963740821276</v>
+        <v>0.2433596808168664</v>
       </c>
       <c r="T90">
-        <v>3.435331297087643</v>
+        <v>3.747634142277429</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08483741757782466</v>
+        <v>0.08388418816683788</v>
       </c>
       <c r="W90">
-        <v>0.2157953369351489</v>
+        <v>0.2160201084302596</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4241870878891233</v>
+        <v>0.4194209408341893</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2190274613927864</v>
+        <v>0.2209274613927864</v>
       </c>
       <c r="C91">
-        <v>-1080.184023644185</v>
+        <v>-1105.002078857585</v>
       </c>
       <c r="D91">
-        <v>574.0479763558153</v>
+        <v>569.0179211424147</v>
       </c>
       <c r="E91">
-        <v>688.8320000000001</v>
+        <v>708.6200000000001</v>
       </c>
       <c r="F91">
-        <v>1761.132</v>
+        <v>1780.92</v>
       </c>
       <c r="G91">
         <v>106.9</v>
@@ -8737,37 +8737,37 @@
         <v>174.175</v>
       </c>
       <c r="M91">
-        <v>415.2749256</v>
+        <v>419.940936</v>
       </c>
       <c r="N91">
-        <v>-241.0999256</v>
+        <v>-245.765936</v>
       </c>
       <c r="O91">
-        <v>-48.21998512000001</v>
+        <v>-49.15318720000001</v>
       </c>
       <c r="P91">
-        <v>-192.87994048</v>
+        <v>-196.6127488</v>
       </c>
       <c r="Q91">
-        <v>-164.17994048</v>
+        <v>-167.9127488</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2433596808168664</v>
+        <v>0.2631156488985532</v>
       </c>
       <c r="T91">
-        <v>3.747634142277429</v>
+        <v>4.122397556505173</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08388418816683788</v>
+        <v>0.08295214163165078</v>
       </c>
       <c r="W91">
-        <v>0.2160201084302596</v>
+        <v>0.2162398850032567</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4194209408341893</v>
+        <v>0.4147607081582539</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2209274613927864</v>
+        <v>0.2228274613927864</v>
       </c>
       <c r="C92">
-        <v>-1105.002078857585</v>
+        <v>-1129.732748765136</v>
       </c>
       <c r="D92">
-        <v>569.0179211424147</v>
+        <v>564.075251234864</v>
       </c>
       <c r="E92">
-        <v>708.6200000000001</v>
+        <v>728.4080000000001</v>
       </c>
       <c r="F92">
-        <v>1780.92</v>
+        <v>1800.708</v>
       </c>
       <c r="G92">
         <v>106.9</v>
@@ -8819,37 +8819,37 @@
         <v>174.175</v>
       </c>
       <c r="M92">
-        <v>419.940936</v>
+        <v>424.6069464</v>
       </c>
       <c r="N92">
-        <v>-245.765936</v>
+        <v>-250.4319464</v>
       </c>
       <c r="O92">
-        <v>-49.15318720000001</v>
+        <v>-50.08638928000001</v>
       </c>
       <c r="P92">
-        <v>-196.6127488</v>
+        <v>-200.34555712</v>
       </c>
       <c r="Q92">
-        <v>-167.9127488</v>
+        <v>-171.64555712</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2631156488985532</v>
+        <v>0.2872618321095035</v>
       </c>
       <c r="T92">
-        <v>4.122397556505173</v>
+        <v>4.580441729450192</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08295214163165078</v>
+        <v>0.08204057963569858</v>
       </c>
       <c r="W92">
-        <v>0.2162398850032567</v>
+        <v>0.2164548313219023</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4147607081582539</v>
+        <v>0.4102028981784929</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2228274613927864</v>
+        <v>0.2247274613927864</v>
       </c>
       <c r="C93">
-        <v>-1129.732748765136</v>
+        <v>-1154.378290926301</v>
       </c>
       <c r="D93">
-        <v>564.075251234864</v>
+        <v>559.2177090736986</v>
       </c>
       <c r="E93">
-        <v>728.4080000000001</v>
+        <v>748.1960000000001</v>
       </c>
       <c r="F93">
-        <v>1800.708</v>
+        <v>1820.496</v>
       </c>
       <c r="G93">
         <v>106.9</v>
@@ -8901,37 +8901,37 @@
         <v>174.175</v>
       </c>
       <c r="M93">
-        <v>424.6069464</v>
+        <v>429.2729568</v>
       </c>
       <c r="N93">
-        <v>-250.4319464</v>
+        <v>-255.0979568</v>
       </c>
       <c r="O93">
-        <v>-50.08638928000001</v>
+        <v>-51.01959136000001</v>
       </c>
       <c r="P93">
-        <v>-200.34555712</v>
+        <v>-204.07836544</v>
       </c>
       <c r="Q93">
-        <v>-171.64555712</v>
+        <v>-175.37836544</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2872618321095035</v>
+        <v>0.3174445611231915</v>
       </c>
       <c r="T93">
-        <v>4.580441729450192</v>
+        <v>5.152996945631467</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08204057963569858</v>
+        <v>0.08114883420487577</v>
       </c>
       <c r="W93">
-        <v>0.2164548313219023</v>
+        <v>0.2166651048944903</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4102028981784929</v>
+        <v>0.4057441710243788</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2247274613927864</v>
+        <v>0.2266274613927864</v>
       </c>
       <c r="C94">
-        <v>-1154.378290926301</v>
+        <v>-1178.940885800471</v>
       </c>
       <c r="D94">
-        <v>559.2177090736986</v>
+        <v>554.4431141995288</v>
       </c>
       <c r="E94">
-        <v>748.1960000000001</v>
+        <v>767.9840000000002</v>
       </c>
       <c r="F94">
-        <v>1820.496</v>
+        <v>1840.284</v>
       </c>
       <c r="G94">
         <v>106.9</v>
@@ -8983,37 +8983,37 @@
         <v>174.175</v>
       </c>
       <c r="M94">
-        <v>429.2729568</v>
+        <v>433.9389672</v>
       </c>
       <c r="N94">
-        <v>-255.0979568</v>
+        <v>-259.7639672</v>
       </c>
       <c r="O94">
-        <v>-51.01959136000001</v>
+        <v>-51.95279344000001</v>
       </c>
       <c r="P94">
-        <v>-204.07836544</v>
+        <v>-207.81117376</v>
       </c>
       <c r="Q94">
-        <v>-175.37836544</v>
+        <v>-179.11117376</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3174445611231915</v>
+        <v>0.3562509269979332</v>
       </c>
       <c r="T94">
-        <v>5.152996945631467</v>
+        <v>5.889139366435963</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08114883420487577</v>
+        <v>0.08027626609514592</v>
       </c>
       <c r="W94">
-        <v>0.2166651048944903</v>
+        <v>0.2168708564547646</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4057441710243788</v>
+        <v>0.4013813304757297</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2266274613927864</v>
+        <v>0.2285274613927864</v>
       </c>
       <c r="C95">
-        <v>-1178.940885800471</v>
+        <v>-1203.422640010494</v>
       </c>
       <c r="D95">
-        <v>554.4431141995288</v>
+        <v>549.7493599895059</v>
       </c>
       <c r="E95">
-        <v>767.9840000000002</v>
+        <v>787.7720000000002</v>
       </c>
       <c r="F95">
-        <v>1840.284</v>
+        <v>1860.072</v>
       </c>
       <c r="G95">
         <v>106.9</v>
@@ -9065,37 +9065,37 @@
         <v>174.175</v>
       </c>
       <c r="M95">
-        <v>433.9389672</v>
+        <v>438.6049776</v>
       </c>
       <c r="N95">
-        <v>-259.7639672</v>
+        <v>-264.4299776</v>
       </c>
       <c r="O95">
-        <v>-51.95279344000001</v>
+        <v>-52.88599552000001</v>
       </c>
       <c r="P95">
-        <v>-207.81117376</v>
+        <v>-211.54398208</v>
       </c>
       <c r="Q95">
-        <v>-179.11117376</v>
+        <v>-182.84398208</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3562509269979332</v>
+        <v>0.4079927481642555</v>
       </c>
       <c r="T95">
-        <v>5.889139366435963</v>
+        <v>6.870662594175293</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08027626609514592</v>
+        <v>0.07942226326434648</v>
       </c>
       <c r="W95">
-        <v>0.2168708564547646</v>
+        <v>0.2170722303222671</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4013813304757297</v>
+        <v>0.3971113163217325</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2285274613927864</v>
+        <v>0.2304274613927864</v>
       </c>
       <c r="C96">
-        <v>-1203.422640010494</v>
+        <v>-1227.825589441835</v>
       </c>
       <c r="D96">
-        <v>549.7493599895059</v>
+        <v>545.1344105581655</v>
       </c>
       <c r="E96">
-        <v>787.7720000000002</v>
+        <v>807.5600000000002</v>
       </c>
       <c r="F96">
-        <v>1860.072</v>
+        <v>1879.86</v>
       </c>
       <c r="G96">
         <v>106.9</v>
@@ -9147,37 +9147,37 @@
         <v>174.175</v>
       </c>
       <c r="M96">
-        <v>438.6049776</v>
+        <v>443.270988</v>
       </c>
       <c r="N96">
-        <v>-264.4299776</v>
+        <v>-269.095988</v>
       </c>
       <c r="O96">
-        <v>-52.88599552000001</v>
+        <v>-53.81919760000001</v>
       </c>
       <c r="P96">
-        <v>-211.54398208</v>
+        <v>-215.2767904</v>
       </c>
       <c r="Q96">
-        <v>-182.84398208</v>
+        <v>-186.5767904</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4079927481642555</v>
+        <v>0.4804312977971069</v>
       </c>
       <c r="T96">
-        <v>6.870662594175293</v>
+        <v>8.244795113010357</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07942226326434648</v>
+        <v>0.07858623944051127</v>
       </c>
       <c r="W96">
-        <v>0.2170722303222671</v>
+        <v>0.2172693647399274</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3971113163217325</v>
+        <v>0.3929311972025563</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2304274613927864</v>
+        <v>0.2323274613927864</v>
       </c>
       <c r="C97">
-        <v>-1227.825589441835</v>
+        <v>-1252.151702186931</v>
       </c>
       <c r="D97">
-        <v>545.1344105581655</v>
+        <v>540.5962978130688</v>
       </c>
       <c r="E97">
-        <v>807.5600000000002</v>
+        <v>827.3480000000002</v>
       </c>
       <c r="F97">
-        <v>1879.86</v>
+        <v>1899.648</v>
       </c>
       <c r="G97">
         <v>106.9</v>
@@ -9229,37 +9229,37 @@
         <v>174.175</v>
       </c>
       <c r="M97">
-        <v>443.270988</v>
+        <v>447.9369984</v>
       </c>
       <c r="N97">
-        <v>-269.095988</v>
+        <v>-273.7619984</v>
       </c>
       <c r="O97">
-        <v>-53.81919760000001</v>
+        <v>-54.75239968000001</v>
       </c>
       <c r="P97">
-        <v>-215.2767904</v>
+        <v>-219.00959872</v>
       </c>
       <c r="Q97">
-        <v>-186.5767904</v>
+        <v>-190.30959872</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4804312977971069</v>
+        <v>0.5890891222463837</v>
       </c>
       <c r="T97">
-        <v>8.244795113010357</v>
+        <v>10.30599389126295</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07858623944051127</v>
+        <v>0.07776763277967261</v>
       </c>
       <c r="W97">
-        <v>0.2172693647399274</v>
+        <v>0.2174623921905532</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3929311972025563</v>
+        <v>0.388838163898363</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2323274613927864</v>
+        <v>0.2342274613927864</v>
       </c>
       <c r="C98">
-        <v>-1252.151702186931</v>
+        <v>-1276.402881343703</v>
       </c>
       <c r="D98">
-        <v>540.5962978130688</v>
+        <v>536.1331186562965</v>
       </c>
       <c r="E98">
-        <v>827.348</v>
+        <v>847.136</v>
       </c>
       <c r="F98">
-        <v>1899.648</v>
+        <v>1919.436</v>
       </c>
       <c r="G98">
         <v>106.9</v>
@@ -9311,37 +9311,37 @@
         <v>174.175</v>
       </c>
       <c r="M98">
-        <v>447.9369984</v>
+        <v>452.6030088</v>
       </c>
       <c r="N98">
-        <v>-273.7619984</v>
+        <v>-278.4280088</v>
       </c>
       <c r="O98">
-        <v>-54.75239968000001</v>
+        <v>-55.68560176000001</v>
       </c>
       <c r="P98">
-        <v>-219.00959872</v>
+        <v>-222.74240704</v>
       </c>
       <c r="Q98">
-        <v>-190.30959872</v>
+        <v>-194.04240704</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5890891222463822</v>
+        <v>0.7701854963285096</v>
       </c>
       <c r="T98">
-        <v>10.30599389126292</v>
+        <v>13.74132518835056</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07776763277967262</v>
+        <v>0.0769659046066863</v>
       </c>
       <c r="W98">
-        <v>0.2174623921905532</v>
+        <v>0.2176514396937434</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.388838163898363</v>
+        <v>0.3848295230334314</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2342274613927864</v>
+        <v>0.2361274613927864</v>
       </c>
       <c r="C99">
-        <v>-1276.402881343703</v>
+        <v>-1300.580967676566</v>
       </c>
       <c r="D99">
-        <v>536.1331186562965</v>
+        <v>531.7430323234344</v>
       </c>
       <c r="E99">
-        <v>847.136</v>
+        <v>866.924</v>
       </c>
       <c r="F99">
-        <v>1919.436</v>
+        <v>1939.224</v>
       </c>
       <c r="G99">
         <v>106.9</v>
@@ -9393,37 +9393,37 @@
         <v>174.175</v>
       </c>
       <c r="M99">
-        <v>452.6030088</v>
+        <v>457.2690192</v>
       </c>
       <c r="N99">
-        <v>-278.4280088</v>
+        <v>-283.0940192</v>
       </c>
       <c r="O99">
-        <v>-55.68560176000001</v>
+        <v>-56.61880384000001</v>
       </c>
       <c r="P99">
-        <v>-222.74240704</v>
+        <v>-226.47521536</v>
       </c>
       <c r="Q99">
-        <v>-194.04240704</v>
+        <v>-197.77521536</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7701854963285096</v>
+        <v>1.132378244492765</v>
       </c>
       <c r="T99">
-        <v>13.74132518835056</v>
+        <v>20.61198778252584</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0769659046066863</v>
+        <v>0.07618053823314869</v>
       </c>
       <c r="W99">
-        <v>0.2176514396937434</v>
+        <v>0.2178366290846236</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3848295230334314</v>
+        <v>0.3809026911657433</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2361274613927864</v>
+        <v>0.2380274613927864</v>
       </c>
       <c r="C100">
-        <v>-1300.580967676566</v>
+        <v>-1324.687742147764</v>
       </c>
       <c r="D100">
-        <v>531.7430323234344</v>
+        <v>527.4242578522359</v>
       </c>
       <c r="E100">
-        <v>866.924</v>
+        <v>886.712</v>
       </c>
       <c r="F100">
-        <v>1939.224</v>
+        <v>1959.012</v>
       </c>
       <c r="G100">
         <v>106.9</v>
@@ -9475,37 +9475,37 @@
         <v>174.175</v>
       </c>
       <c r="M100">
-        <v>457.2690192</v>
+        <v>461.9350296</v>
       </c>
       <c r="N100">
-        <v>-283.0940192</v>
+        <v>-287.7600296000001</v>
       </c>
       <c r="O100">
-        <v>-56.61880384000001</v>
+        <v>-57.55200592000001</v>
       </c>
       <c r="P100">
-        <v>-226.47521536</v>
+        <v>-230.2080236800001</v>
       </c>
       <c r="Q100">
-        <v>-197.77521536</v>
+        <v>-201.50802368</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.132378244492765</v>
+        <v>2.218956488985529</v>
       </c>
       <c r="T100">
-        <v>20.61198778252584</v>
+        <v>41.22397556505168</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07618053823314869</v>
+        <v>0.07541103784695526</v>
       </c>
       <c r="W100">
-        <v>0.2178366290846236</v>
+        <v>0.2180180772756879</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3809026911657433</v>
+        <v>0.3770551892347762</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2380274613927864</v>
-      </c>
-      <c r="C101">
-        <v>-1324.687742147764</v>
-      </c>
-      <c r="D101">
-        <v>527.4242578522359</v>
-      </c>
-      <c r="E101">
-        <v>886.712</v>
-      </c>
-      <c r="F101">
-        <v>1959.012</v>
-      </c>
-      <c r="G101">
-        <v>106.9</v>
-      </c>
-      <c r="H101">
-        <v>906.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>202.875</v>
-      </c>
-      <c r="K101">
-        <v>28.70000000000002</v>
-      </c>
-      <c r="L101">
-        <v>174.175</v>
-      </c>
-      <c r="M101">
-        <v>461.9350296</v>
-      </c>
-      <c r="N101">
-        <v>-287.7600296000001</v>
-      </c>
-      <c r="O101">
-        <v>-57.55200592000001</v>
-      </c>
-      <c r="P101">
-        <v>-230.2080236800001</v>
-      </c>
-      <c r="Q101">
-        <v>-201.50802368</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.218956488985529</v>
-      </c>
-      <c r="T101">
-        <v>41.22397556505168</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07541103784695526</v>
-      </c>
-      <c r="W101">
-        <v>0.2180180772756879</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3770551892347762</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
